--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -276,12 +276,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$45</f>
+              <f>'루나시트 VR일지'!$B$8:$B$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$E$8:$E$45</f>
+              <f>'루나시트 VR일지'!$E$8:$E$46</f>
             </numRef>
           </val>
         </ser>
@@ -308,12 +308,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$45</f>
+              <f>'루나시트 VR일지'!$B$8:$B$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$F$8:$F$45</f>
+              <f>'루나시트 VR일지'!$F$8:$F$46</f>
             </numRef>
           </val>
         </ser>
@@ -340,12 +340,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$45</f>
+              <f>'루나시트 VR일지'!$B$8:$B$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$G$8:$G$45</f>
+              <f>'루나시트 VR일지'!$G$8:$G$46</f>
             </numRef>
           </val>
         </ser>
@@ -730,15 +730,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -798,22 +798,22 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="3" t="n">
-        <v>15376.77</v>
+        <v>19811.82</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14870.71</v>
+        <v>14448.79</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>506.06</v>
+        <v>5363.029999999999</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>4389.77135</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3792.9772757375</v>
+        <v>4205.8197257375</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>5131.6751377625</v>
+        <v>5690.2266877625</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2053,7 +2053,64 @@
         <v>10408.38</v>
       </c>
     </row>
-    <row r="46"/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2회차 (9/14일)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>208</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>14448.79</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>5363.03</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>19811.82</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>4389.77</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>1.2217</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>/10</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="L46" s="6" t="n">
+        <v>4948.02</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>4205.82</v>
+      </c>
+      <c r="N46" s="6" t="n">
+        <v>5690.23</v>
+      </c>
+      <c r="O46" s="18" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v>9500.77</v>
+      </c>
+    </row>
     <row r="47"/>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -2068,94 +2125,110 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>🟢 [매수 30단계 차등가이드]</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>지정가($)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>할당금액($)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>수량(주)</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>🔴 [매도 30단계 차등가이드]</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>지정가($)</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>할당금액($)</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>수량(주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>회차</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>지정가($)</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>할당금액($)</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>수량(주)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>회차</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J50" s="16" t="inlineStr">
         <is>
           <t>지정가($)</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K50" s="16" t="inlineStr">
         <is>
           <t>할당금액($)</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L50" s="17" t="inlineStr">
         <is>
           <t>수량(주)</t>
         </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B50" s="12" t="n">
-        <v>70.98999999999999</v>
-      </c>
-      <c r="C50" s="12" t="n">
-        <v>70.98999999999999</v>
-      </c>
-      <c r="D50" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>75.89</v>
-      </c>
-      <c r="K50" s="12" t="n">
-        <v>455.37</v>
-      </c>
-      <c r="L50" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" s="12" t="n">
-        <v>69.91</v>
+        <v>68.31</v>
       </c>
       <c r="C51" s="12" t="n">
-        <v>69.91</v>
+        <v>68.31</v>
       </c>
       <c r="D51" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>79.13</v>
+        <v>73.03</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>474.79</v>
+        <v>438.18</v>
       </c>
       <c r="L51" s="13" t="n">
         <v>6</v>
@@ -2163,25 +2236,25 @@
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" s="12" t="n">
-        <v>68.83</v>
+        <v>67.27</v>
       </c>
       <c r="C52" s="12" t="n">
-        <v>68.83</v>
+        <v>67.27</v>
       </c>
       <c r="D52" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>82.51000000000001</v>
+        <v>76.14</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>495.03</v>
+        <v>456.87</v>
       </c>
       <c r="L52" s="13" t="n">
         <v>6</v>
@@ -2189,25 +2262,25 @@
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" s="12" t="n">
-        <v>67.75</v>
+        <v>66.23</v>
       </c>
       <c r="C53" s="12" t="n">
-        <v>67.75</v>
+        <v>132.46</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>86.02</v>
+        <v>79.39</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>516.14</v>
+        <v>476.35</v>
       </c>
       <c r="L53" s="13" t="n">
         <v>6</v>
@@ -2215,25 +2288,25 @@
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B54" s="12" t="n">
-        <v>66.66</v>
+        <v>65.19</v>
       </c>
       <c r="C54" s="12" t="n">
-        <v>66.66</v>
+        <v>130.38</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>89.69</v>
+        <v>82.78</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>538.15</v>
+        <v>496.66</v>
       </c>
       <c r="L54" s="13" t="n">
         <v>6</v>
@@ -2241,25 +2314,25 @@
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B55" s="12" t="n">
-        <v>65.58</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="C55" s="12" t="n">
-        <v>65.58</v>
+        <v>128.3</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>93.52</v>
+        <v>86.31</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>561.1</v>
+        <v>517.84</v>
       </c>
       <c r="L55" s="13" t="n">
         <v>6</v>
@@ -2267,25 +2340,25 @@
     </row>
     <row r="56">
       <c r="A56" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B56" s="12" t="n">
-        <v>64.5</v>
+        <v>63.11</v>
       </c>
       <c r="C56" s="12" t="n">
-        <v>64.5</v>
+        <v>126.22</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>97.5</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>585.03</v>
+        <v>539.92</v>
       </c>
       <c r="L56" s="13" t="n">
         <v>6</v>
@@ -2293,25 +2366,25 @@
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B57" s="12" t="n">
-        <v>63.42</v>
+        <v>62.07</v>
       </c>
       <c r="C57" s="12" t="n">
-        <v>63.42</v>
+        <v>124.14</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>101.66</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>609.97</v>
+        <v>562.95</v>
       </c>
       <c r="L57" s="13" t="n">
         <v>6</v>
@@ -2319,25 +2392,25 @@
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" s="12" t="n">
-        <v>62.34</v>
+        <v>61.03</v>
       </c>
       <c r="C58" s="12" t="n">
-        <v>62.34</v>
+        <v>122.06</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>106</v>
+        <v>97.83</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>635.99</v>
+        <v>586.95</v>
       </c>
       <c r="L58" s="13" t="n">
         <v>6</v>
@@ -2345,25 +2418,25 @@
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B59" s="12" t="n">
-        <v>61.26</v>
+        <v>59.99</v>
       </c>
       <c r="C59" s="12" t="n">
-        <v>61.26</v>
+        <v>119.98</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>110.52</v>
+        <v>102</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>663.11</v>
+        <v>611.98</v>
       </c>
       <c r="L59" s="13" t="n">
         <v>6</v>
@@ -2371,25 +2444,25 @@
     </row>
     <row r="60">
       <c r="A60" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" s="12" t="n">
-        <v>60.18</v>
+        <v>58.95</v>
       </c>
       <c r="C60" s="12" t="n">
-        <v>60.18</v>
+        <v>117.89</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>115.23</v>
+        <v>106.35</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>691.38</v>
+        <v>638.08</v>
       </c>
       <c r="L60" s="13" t="n">
         <v>6</v>
@@ -2397,25 +2470,25 @@
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61" s="12" t="n">
-        <v>59.1</v>
+        <v>57.91</v>
       </c>
       <c r="C61" s="12" t="n">
-        <v>59.1</v>
+        <v>115.81</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>120.14</v>
+        <v>110.88</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>720.87</v>
+        <v>665.29</v>
       </c>
       <c r="L61" s="13" t="n">
         <v>6</v>
@@ -2423,25 +2496,25 @@
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B62" s="12" t="n">
-        <v>58.02</v>
+        <v>56.87</v>
       </c>
       <c r="C62" s="12" t="n">
-        <v>58.02</v>
+        <v>113.73</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>125.27</v>
+        <v>115.61</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>751.61</v>
+        <v>693.66</v>
       </c>
       <c r="L62" s="13" t="n">
         <v>6</v>
@@ -2449,25 +2522,25 @@
     </row>
     <row r="63">
       <c r="A63" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B63" s="12" t="n">
-        <v>56.94</v>
+        <v>55.83</v>
       </c>
       <c r="C63" s="12" t="n">
-        <v>56.94</v>
+        <v>111.65</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>130.61</v>
+        <v>120.54</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>783.66</v>
+        <v>723.24</v>
       </c>
       <c r="L63" s="13" t="n">
         <v>6</v>
@@ -2475,25 +2548,25 @@
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B64" s="12" t="n">
-        <v>55.85</v>
+        <v>54.79</v>
       </c>
       <c r="C64" s="12" t="n">
-        <v>55.85</v>
+        <v>109.57</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>136.18</v>
+        <v>125.68</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>817.0700000000001</v>
+        <v>754.08</v>
       </c>
       <c r="L64" s="13" t="n">
         <v>6</v>
@@ -2501,25 +2574,25 @@
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B65" s="12" t="n">
-        <v>54.77</v>
+        <v>53.75</v>
       </c>
       <c r="C65" s="12" t="n">
-        <v>54.77</v>
+        <v>107.49</v>
       </c>
       <c r="D65" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>141.99</v>
+        <v>131.04</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>851.92</v>
+        <v>786.24</v>
       </c>
       <c r="L65" s="13" t="n">
         <v>6</v>
@@ -2527,25 +2600,25 @@
     </row>
     <row r="66">
       <c r="A66" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B66" s="12" t="n">
-        <v>53.69</v>
+        <v>52.71</v>
       </c>
       <c r="C66" s="12" t="n">
-        <v>53.69</v>
+        <v>105.41</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>148.04</v>
+        <v>136.63</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>888.24</v>
+        <v>819.76</v>
       </c>
       <c r="L66" s="13" t="n">
         <v>6</v>
@@ -2553,25 +2626,25 @@
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B67" s="12" t="n">
-        <v>52.61</v>
+        <v>51.67</v>
       </c>
       <c r="C67" s="12" t="n">
-        <v>52.61</v>
+        <v>103.33</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>154.35</v>
+        <v>142.45</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>926.12</v>
+        <v>854.72</v>
       </c>
       <c r="L67" s="13" t="n">
         <v>6</v>
@@ -2579,25 +2652,25 @@
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B68" s="12" t="n">
-        <v>51.53</v>
+        <v>50.63</v>
       </c>
       <c r="C68" s="12" t="n">
-        <v>51.53</v>
+        <v>101.25</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>160.94</v>
+        <v>148.53</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>965.61</v>
+        <v>891.17</v>
       </c>
       <c r="L68" s="13" t="n">
         <v>6</v>
@@ -2605,25 +2678,25 @@
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B69" s="12" t="n">
-        <v>50.45</v>
+        <v>49.59</v>
       </c>
       <c r="C69" s="12" t="n">
-        <v>50.45</v>
+        <v>99.17</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>167.8</v>
+        <v>154.86</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>1006.79</v>
+        <v>929.17</v>
       </c>
       <c r="L69" s="13" t="n">
         <v>6</v>
@@ -2631,25 +2704,25 @@
     </row>
     <row r="70">
       <c r="A70" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B70" s="12" t="n">
-        <v>49.37</v>
+        <v>48.54</v>
       </c>
       <c r="C70" s="12" t="n">
-        <v>49.37</v>
+        <v>97.09</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>174.95</v>
+        <v>161.47</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>1049.72</v>
+        <v>968.79</v>
       </c>
       <c r="L70" s="13" t="n">
         <v>6</v>
@@ -2657,25 +2730,25 @@
     </row>
     <row r="71">
       <c r="A71" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B71" s="12" t="n">
-        <v>48.29</v>
+        <v>47.5</v>
       </c>
       <c r="C71" s="12" t="n">
-        <v>48.29</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>182.41</v>
+        <v>168.35</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>1094.49</v>
+        <v>1010.11</v>
       </c>
       <c r="L71" s="13" t="n">
         <v>6</v>
@@ -2683,25 +2756,25 @@
     </row>
     <row r="72">
       <c r="A72" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B72" s="12" t="n">
-        <v>47.21</v>
+        <v>46.46</v>
       </c>
       <c r="C72" s="12" t="n">
-        <v>47.21</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>190.19</v>
+        <v>175.53</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>1141.16</v>
+        <v>1053.18</v>
       </c>
       <c r="L72" s="13" t="n">
         <v>6</v>
@@ -2709,25 +2782,25 @@
     </row>
     <row r="73">
       <c r="A73" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B73" s="12" t="n">
-        <v>46.12</v>
+        <v>45.42</v>
       </c>
       <c r="C73" s="12" t="n">
-        <v>46.12</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>198.3</v>
+        <v>183.01</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1189.82</v>
+        <v>1098.09</v>
       </c>
       <c r="L73" s="13" t="n">
         <v>6</v>
@@ -2735,25 +2808,25 @@
     </row>
     <row r="74">
       <c r="A74" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B74" s="12" t="n">
-        <v>45.04</v>
+        <v>44.38</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>45.04</v>
+        <v>133.15</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>206.76</v>
+        <v>190.82</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>1240.56</v>
+        <v>1144.92</v>
       </c>
       <c r="L74" s="13" t="n">
         <v>6</v>
@@ -2761,25 +2834,25 @@
     </row>
     <row r="75">
       <c r="A75" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B75" s="12" t="n">
-        <v>43.96</v>
+        <v>43.34</v>
       </c>
       <c r="C75" s="12" t="n">
-        <v>43.96</v>
+        <v>130.03</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I75" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>215.58</v>
+        <v>198.96</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>1293.46</v>
+        <v>1193.74</v>
       </c>
       <c r="L75" s="13" t="n">
         <v>6</v>
@@ -2787,25 +2860,25 @@
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B76" s="12" t="n">
-        <v>42.88</v>
+        <v>42.3</v>
       </c>
       <c r="C76" s="12" t="n">
-        <v>42.88</v>
+        <v>126.91</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I76" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>224.77</v>
+        <v>207.44</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>1348.62</v>
+        <v>1244.64</v>
       </c>
       <c r="L76" s="13" t="n">
         <v>6</v>
@@ -2813,25 +2886,25 @@
     </row>
     <row r="77">
       <c r="A77" s="11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B77" s="12" t="n">
-        <v>41.8</v>
+        <v>41.26</v>
       </c>
       <c r="C77" s="12" t="n">
-        <v>41.8</v>
+        <v>123.79</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I77" s="11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>234.35</v>
+        <v>216.29</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>1406.13</v>
+        <v>1297.72</v>
       </c>
       <c r="L77" s="13" t="n">
         <v>6</v>
@@ -2839,25 +2912,25 @@
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B78" s="12" t="n">
-        <v>40.72</v>
+        <v>40.22</v>
       </c>
       <c r="C78" s="12" t="n">
-        <v>40.72</v>
+        <v>120.67</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>244.35</v>
+        <v>225.51</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>1466.09</v>
+        <v>1353.06</v>
       </c>
       <c r="L78" s="13" t="n">
         <v>6</v>
@@ -2865,27 +2938,53 @@
     </row>
     <row r="79">
       <c r="A79" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="C79" s="12" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="D79" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="J79" s="12" t="n">
+        <v>235.13</v>
+      </c>
+      <c r="K79" s="12" t="n">
+        <v>1410.75</v>
+      </c>
+      <c r="L79" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="B79" s="12" t="n">
-        <v>39.64</v>
-      </c>
-      <c r="C79" s="12" t="n">
-        <v>39.64</v>
-      </c>
-      <c r="D79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" s="11" t="n">
+      <c r="B80" s="12" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="C80" s="12" t="n">
+        <v>114.43</v>
+      </c>
+      <c r="D80" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="J79" s="12" t="n">
-        <v>254.77</v>
-      </c>
-      <c r="K79" s="12" t="n">
-        <v>1528.6</v>
-      </c>
-      <c r="L79" s="13" t="n">
+      <c r="J80" s="12" t="n">
+        <v>245.15</v>
+      </c>
+      <c r="K80" s="12" t="n">
+        <v>1470.91</v>
+      </c>
+      <c r="L80" s="13" t="n">
         <v>6</v>
       </c>
     </row>

--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -276,12 +276,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$46</f>
+              <f>'루나시트 VR일지'!$B$8:$B$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$E$8:$E$46</f>
+              <f>'루나시트 VR일지'!$E$8:$E$47</f>
             </numRef>
           </val>
         </ser>
@@ -308,12 +308,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$46</f>
+              <f>'루나시트 VR일지'!$B$8:$B$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$F$8:$F$46</f>
+              <f>'루나시트 VR일지'!$F$8:$F$47</f>
             </numRef>
           </val>
         </ser>
@@ -340,12 +340,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$46</f>
+              <f>'루나시트 VR일지'!$B$8:$B$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$G$8:$G$46</f>
+              <f>'루나시트 VR일지'!$G$8:$G$47</f>
             </numRef>
           </val>
         </ser>
@@ -730,15 +730,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -798,22 +798,22 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="3" t="n">
-        <v>19811.82</v>
+        <v>20140.31</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14448.79</v>
+        <v>14913.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5363.029999999999</v>
+        <v>5227.110000000001</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>4389.77135</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4205.8197257375</v>
+        <v>4194.2665257375</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>5690.2266877625</v>
+        <v>5674.5958877625</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2111,7 +2111,64 @@
         <v>9500.77</v>
       </c>
     </row>
-    <row r="47"/>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>3회차 (1/14일)</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>210</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>14913.2</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>5227.11</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>20140.31</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>4389.77</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>1.1907</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>/10</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="L47" s="6" t="n">
+        <v>4934.43</v>
+      </c>
+      <c r="M47" s="6" t="n">
+        <v>4194.27</v>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>5674.6</v>
+      </c>
+      <c r="O47" s="18" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v>9978.77</v>
+      </c>
+    </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
@@ -2167,825 +2224,867 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>🟢 [매수 30단계 차등가이드]</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>지정가($)</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>할당금액($)</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>수량(주)</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>🔴 [매도 30단계 차등가이드]</t>
+        </is>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>지정가($)</t>
+        </is>
+      </c>
+      <c r="K50" s="16" t="inlineStr">
+        <is>
+          <t>할당금액($)</t>
+        </is>
+      </c>
+      <c r="L50" s="17" t="inlineStr">
+        <is>
+          <t>수량(주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>회차</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>지정가($)</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>할당금액($)</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>수량(주)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>회차</t>
         </is>
       </c>
-      <c r="J50" s="16" t="inlineStr">
+      <c r="J51" s="16" t="inlineStr">
         <is>
           <t>지정가($)</t>
         </is>
       </c>
-      <c r="K50" s="16" t="inlineStr">
+      <c r="K51" s="16" t="inlineStr">
         <is>
           <t>할당금액($)</t>
         </is>
       </c>
-      <c r="L50" s="17" t="inlineStr">
+      <c r="L51" s="17" t="inlineStr">
         <is>
           <t>수량(주)</t>
         </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B51" s="12" t="n">
-        <v>68.31</v>
-      </c>
-      <c r="C51" s="12" t="n">
-        <v>68.31</v>
-      </c>
-      <c r="D51" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>73.03</v>
-      </c>
-      <c r="K51" s="12" t="n">
-        <v>438.18</v>
-      </c>
-      <c r="L51" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" s="12" t="n">
-        <v>67.27</v>
+        <v>69.84</v>
       </c>
       <c r="C52" s="12" t="n">
-        <v>67.27</v>
+        <v>69.84</v>
       </c>
       <c r="D52" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>76.14</v>
+        <v>74.66</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>456.87</v>
+        <v>522.64</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" s="12" t="n">
-        <v>66.23</v>
+        <v>68.77</v>
       </c>
       <c r="C53" s="12" t="n">
-        <v>132.46</v>
+        <v>68.77</v>
       </c>
       <c r="D53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="I53" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="J53" s="12" t="n">
-        <v>79.39</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>476.35</v>
+        <v>544.9299999999999</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54" s="12" t="n">
-        <v>65.19</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="C54" s="12" t="n">
-        <v>130.38</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>82.78</v>
+        <v>81.17</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>496.66</v>
+        <v>568.16</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B55" s="12" t="n">
-        <v>64.15000000000001</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="C55" s="12" t="n">
-        <v>128.3</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>86.31</v>
+        <v>84.63</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>517.84</v>
+        <v>592.39</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B56" s="12" t="n">
-        <v>63.11</v>
+        <v>65.58</v>
       </c>
       <c r="C56" s="12" t="n">
-        <v>126.22</v>
+        <v>65.58</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>89.98999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>539.92</v>
+        <v>617.65</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B57" s="12" t="n">
-        <v>62.07</v>
+        <v>64.52</v>
       </c>
       <c r="C57" s="12" t="n">
-        <v>124.14</v>
+        <v>129.04</v>
       </c>
       <c r="D57" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>93.81999999999999</v>
+        <v>92</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>562.95</v>
+        <v>643.99</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B58" s="12" t="n">
-        <v>61.03</v>
+        <v>63.46</v>
       </c>
       <c r="C58" s="12" t="n">
-        <v>122.06</v>
+        <v>126.91</v>
       </c>
       <c r="D58" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>97.83</v>
+        <v>95.92</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>586.95</v>
+        <v>671.45</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B59" s="12" t="n">
-        <v>59.99</v>
+        <v>62.39</v>
       </c>
       <c r="C59" s="12" t="n">
-        <v>119.98</v>
+        <v>124.78</v>
       </c>
       <c r="D59" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>102</v>
+        <v>100.01</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>611.98</v>
+        <v>700.08</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B60" s="12" t="n">
-        <v>58.95</v>
+        <v>61.33</v>
       </c>
       <c r="C60" s="12" t="n">
-        <v>117.89</v>
+        <v>122.66</v>
       </c>
       <c r="D60" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>106.35</v>
+        <v>104.28</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>638.08</v>
+        <v>729.9400000000001</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" s="12" t="n">
-        <v>57.91</v>
+        <v>60.27</v>
       </c>
       <c r="C61" s="12" t="n">
-        <v>115.81</v>
+        <v>120.53</v>
       </c>
       <c r="D61" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>110.88</v>
+        <v>108.72</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>665.29</v>
+        <v>761.0599999999999</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" s="12" t="n">
-        <v>56.87</v>
+        <v>59.2</v>
       </c>
       <c r="C62" s="12" t="n">
-        <v>113.73</v>
+        <v>118.4</v>
       </c>
       <c r="D62" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>115.61</v>
+        <v>113.36</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>693.66</v>
+        <v>793.52</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B63" s="12" t="n">
-        <v>55.83</v>
+        <v>58.14</v>
       </c>
       <c r="C63" s="12" t="n">
-        <v>111.65</v>
+        <v>116.28</v>
       </c>
       <c r="D63" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>120.54</v>
+        <v>118.19</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>723.24</v>
+        <v>827.36</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B64" s="12" t="n">
-        <v>54.79</v>
+        <v>57.07</v>
       </c>
       <c r="C64" s="12" t="n">
-        <v>109.57</v>
+        <v>114.15</v>
       </c>
       <c r="D64" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>125.68</v>
+        <v>123.23</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>754.08</v>
+        <v>862.64</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B65" s="12" t="n">
-        <v>53.75</v>
+        <v>56.01</v>
       </c>
       <c r="C65" s="12" t="n">
-        <v>107.49</v>
+        <v>112.02</v>
       </c>
       <c r="D65" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>131.04</v>
+        <v>128.49</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>786.24</v>
+        <v>899.42</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B66" s="12" t="n">
-        <v>52.71</v>
+        <v>54.95</v>
       </c>
       <c r="C66" s="12" t="n">
-        <v>105.41</v>
+        <v>109.9</v>
       </c>
       <c r="D66" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>136.63</v>
+        <v>133.97</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>819.76</v>
+        <v>937.78</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B67" s="12" t="n">
-        <v>51.67</v>
+        <v>53.88</v>
       </c>
       <c r="C67" s="12" t="n">
-        <v>103.33</v>
+        <v>107.77</v>
       </c>
       <c r="D67" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>142.45</v>
+        <v>139.68</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>854.72</v>
+        <v>977.77</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B68" s="12" t="n">
-        <v>50.63</v>
+        <v>52.82</v>
       </c>
       <c r="C68" s="12" t="n">
-        <v>101.25</v>
+        <v>105.64</v>
       </c>
       <c r="D68" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>148.53</v>
+        <v>145.64</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>891.17</v>
+        <v>1019.46</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B69" s="12" t="n">
-        <v>49.59</v>
+        <v>51.76</v>
       </c>
       <c r="C69" s="12" t="n">
-        <v>99.17</v>
+        <v>103.51</v>
       </c>
       <c r="D69" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>154.86</v>
+        <v>151.85</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>929.17</v>
+        <v>1062.93</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B70" s="12" t="n">
-        <v>48.54</v>
+        <v>50.69</v>
       </c>
       <c r="C70" s="12" t="n">
-        <v>97.09</v>
+        <v>101.39</v>
       </c>
       <c r="D70" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>161.47</v>
+        <v>158.32</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>968.79</v>
+        <v>1108.26</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B71" s="12" t="n">
-        <v>47.5</v>
+        <v>49.63</v>
       </c>
       <c r="C71" s="12" t="n">
-        <v>95.01000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="D71" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>168.35</v>
+        <v>165.07</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>1010.11</v>
+        <v>1155.52</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B72" s="12" t="n">
-        <v>46.46</v>
+        <v>48.57</v>
       </c>
       <c r="C72" s="12" t="n">
-        <v>92.93000000000001</v>
+        <v>97.13</v>
       </c>
       <c r="D72" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>175.53</v>
+        <v>172.11</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>1053.18</v>
+        <v>1204.8</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B73" s="12" t="n">
-        <v>45.42</v>
+        <v>47.5</v>
       </c>
       <c r="C73" s="12" t="n">
-        <v>90.84999999999999</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="D73" s="13" t="n">
         <v>2</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>183.01</v>
+        <v>179.45</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1098.09</v>
+        <v>1256.17</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B74" s="12" t="n">
-        <v>44.38</v>
+        <v>46.44</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>133.15</v>
+        <v>92.88</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>190.82</v>
+        <v>187.11</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>1144.92</v>
+        <v>1309.74</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B75" s="12" t="n">
-        <v>43.34</v>
+        <v>45.38</v>
       </c>
       <c r="C75" s="12" t="n">
-        <v>130.03</v>
+        <v>90.75</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>198.96</v>
+        <v>195.08</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>1193.74</v>
+        <v>1365.59</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B76" s="12" t="n">
-        <v>42.3</v>
+        <v>44.31</v>
       </c>
       <c r="C76" s="12" t="n">
-        <v>126.91</v>
+        <v>88.62</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I76" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>207.44</v>
+        <v>203.4</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>1244.64</v>
+        <v>1423.82</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B77" s="12" t="n">
-        <v>41.26</v>
+        <v>43.25</v>
       </c>
       <c r="C77" s="12" t="n">
-        <v>123.79</v>
+        <v>129.75</v>
       </c>
       <c r="D77" s="13" t="n">
         <v>3</v>
       </c>
       <c r="I77" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>216.29</v>
+        <v>212.08</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>1297.72</v>
+        <v>1484.54</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B78" s="12" t="n">
-        <v>40.22</v>
+        <v>42.19</v>
       </c>
       <c r="C78" s="12" t="n">
-        <v>120.67</v>
+        <v>126.56</v>
       </c>
       <c r="D78" s="13" t="n">
         <v>3</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>225.51</v>
+        <v>221.12</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>1353.06</v>
+        <v>1547.84</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B79" s="12" t="n">
-        <v>39.18</v>
+        <v>41.12</v>
       </c>
       <c r="C79" s="12" t="n">
-        <v>117.55</v>
+        <v>123.37</v>
       </c>
       <c r="D79" s="13" t="n">
         <v>3</v>
       </c>
       <c r="I79" s="11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>235.13</v>
+        <v>230.55</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>1410.75</v>
+        <v>1613.85</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B80" s="12" t="n">
-        <v>38.14</v>
+        <v>40.06</v>
       </c>
       <c r="C80" s="12" t="n">
-        <v>114.43</v>
+        <v>120.18</v>
       </c>
       <c r="D80" s="13" t="n">
         <v>3</v>
       </c>
       <c r="I80" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="J80" s="12" t="n">
+        <v>240.38</v>
+      </c>
+      <c r="K80" s="12" t="n">
+        <v>1682.67</v>
+      </c>
+      <c r="L80" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="J80" s="12" t="n">
-        <v>245.15</v>
-      </c>
-      <c r="K80" s="12" t="n">
-        <v>1470.91</v>
-      </c>
-      <c r="L80" s="13" t="n">
-        <v>6</v>
+      <c r="B81" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="C81" s="12" t="n">
+        <v>116.99</v>
+      </c>
+      <c r="D81" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="J81" s="12" t="n">
+        <v>250.63</v>
+      </c>
+      <c r="K81" s="12" t="n">
+        <v>1754.42</v>
+      </c>
+      <c r="L81" s="13" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -276,12 +276,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$47</f>
+              <f>'루나시트 VR일지'!$B$8:$B$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$E$8:$E$47</f>
+              <f>'루나시트 VR일지'!$E$8:$E$82</f>
             </numRef>
           </val>
         </ser>
@@ -308,12 +308,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$47</f>
+              <f>'루나시트 VR일지'!$B$8:$B$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$F$8:$F$47</f>
+              <f>'루나시트 VR일지'!$F$8:$F$82</f>
             </numRef>
           </val>
         </ser>
@@ -340,12 +340,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$47</f>
+              <f>'루나시트 VR일지'!$B$8:$B$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$G$8:$G$47</f>
+              <f>'루나시트 VR일지'!$G$8:$G$82</f>
             </numRef>
           </val>
         </ser>
@@ -730,16 +730,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -798,22 +798,22 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="3" t="n">
-        <v>20140.31</v>
+        <v>20911.43</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14913.2</v>
+        <v>15684.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5227.110000000001</v>
+        <v>5227.130000000001</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4389.77135</v>
+        <v>4934.43120675</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4194.2665257375</v>
+        <v>4659.543908366188</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>5674.5958877625</v>
+        <v>6304.088817201312</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -3084,6 +3084,900 @@
         <v>1754.42</v>
       </c>
       <c r="L81" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>3회차 (4/14일)</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>210</v>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>15684.3</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>5227.13</v>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>20911.43</v>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>4934.43</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <v>1.0593</v>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>/10</t>
+        </is>
+      </c>
+      <c r="K82" s="8" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="L82" s="6" t="n">
+        <v>5481.82</v>
+      </c>
+      <c r="M82" s="6" t="n">
+        <v>4659.54</v>
+      </c>
+      <c r="N82" s="6" t="n">
+        <v>6304.09</v>
+      </c>
+      <c r="O82" s="18" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="P82" s="6" t="n">
+        <v>10202.48</v>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>🟢 [매수 30단계 차등가이드]</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>🔴 [매도 30단계 차등가이드]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>회차</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>지정가($)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>할당금액($)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>수량(주)</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>회차</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>지정가($)</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>할당금액($)</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>수량(주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" s="12" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="C87" s="12" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="D87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>78.53</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>549.6900000000001</v>
+      </c>
+      <c r="L87" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B88" s="12" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="C88" s="12" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="D88" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" s="12" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="K88" s="12" t="n">
+        <v>573.13</v>
+      </c>
+      <c r="L88" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B89" s="12" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="C89" s="12" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="D89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="K89" s="12" t="n">
+        <v>597.5700000000001</v>
+      </c>
+      <c r="L89" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B90" s="12" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="C90" s="12" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="D90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>623.05</v>
+      </c>
+      <c r="L90" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B91" s="12" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="C91" s="12" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="D91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <v>649.62</v>
+      </c>
+      <c r="L91" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B92" s="12" t="n">
+        <v>67.86</v>
+      </c>
+      <c r="C92" s="12" t="n">
+        <v>67.86</v>
+      </c>
+      <c r="D92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J92" s="12" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="K92" s="12" t="n">
+        <v>677.33</v>
+      </c>
+      <c r="L92" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B93" s="12" t="n">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="C93" s="12" t="n">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="D93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>706.21</v>
+      </c>
+      <c r="L93" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B94" s="12" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="D94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J94" s="12" t="n">
+        <v>105.19</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <v>736.3200000000001</v>
+      </c>
+      <c r="L94" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>129.01</v>
+      </c>
+      <c r="D95" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I95" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <v>109.67</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <v>767.72</v>
+      </c>
+      <c r="L95" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B96" s="12" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>126.77</v>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J96" s="12" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="K96" s="12" t="n">
+        <v>800.46</v>
+      </c>
+      <c r="L96" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B97" s="12" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>124.53</v>
+      </c>
+      <c r="D97" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>119.23</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>834.59</v>
+      </c>
+      <c r="L97" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B98" s="12" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>122.29</v>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>124.31</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>870.1799999999999</v>
+      </c>
+      <c r="L98" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B99" s="12" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>120.06</v>
+      </c>
+      <c r="D99" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>129.61</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>907.29</v>
+      </c>
+      <c r="L99" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B100" s="12" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>117.82</v>
+      </c>
+      <c r="D100" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="J100" s="12" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="K100" s="12" t="n">
+        <v>945.98</v>
+      </c>
+      <c r="L100" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B101" s="12" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>115.58</v>
+      </c>
+      <c r="D101" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I101" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>986.3200000000001</v>
+      </c>
+      <c r="L101" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B102" s="12" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="D102" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>146.91</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>1028.38</v>
+      </c>
+      <c r="L102" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B103" s="12" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="C103" s="12" t="n">
+        <v>111.11</v>
+      </c>
+      <c r="D103" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="J103" s="12" t="n">
+        <v>153.18</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>1072.23</v>
+      </c>
+      <c r="L103" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B104" s="12" t="n">
+        <v>54.44</v>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>108.87</v>
+      </c>
+      <c r="D104" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>159.71</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>1117.96</v>
+      </c>
+      <c r="L104" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B105" s="12" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>106.64</v>
+      </c>
+      <c r="D105" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="J105" s="12" t="n">
+        <v>166.52</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>1165.63</v>
+      </c>
+      <c r="L105" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B106" s="12" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="D106" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>173.62</v>
+      </c>
+      <c r="K106" s="12" t="n">
+        <v>1215.33</v>
+      </c>
+      <c r="L106" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B107" s="12" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="C107" s="12" t="n">
+        <v>102.16</v>
+      </c>
+      <c r="D107" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="J107" s="12" t="n">
+        <v>181.02</v>
+      </c>
+      <c r="K107" s="12" t="n">
+        <v>1267.16</v>
+      </c>
+      <c r="L107" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B108" s="12" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="D108" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="J108" s="12" t="n">
+        <v>188.74</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>1321.19</v>
+      </c>
+      <c r="L108" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B109" s="12" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="D109" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="J109" s="12" t="n">
+        <v>196.79</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>1377.53</v>
+      </c>
+      <c r="L109" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B110" s="12" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="D110" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J110" s="12" t="n">
+        <v>205.18</v>
+      </c>
+      <c r="K110" s="12" t="n">
+        <v>1436.28</v>
+      </c>
+      <c r="L110" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B111" s="12" t="n">
+        <v>46.61</v>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="D111" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="J111" s="12" t="n">
+        <v>213.93</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>1497.52</v>
+      </c>
+      <c r="L111" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B112" s="12" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>90.98</v>
+      </c>
+      <c r="D112" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>223.05</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>1561.38</v>
+      </c>
+      <c r="L112" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B113" s="12" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="C113" s="12" t="n">
+        <v>88.73999999999999</v>
+      </c>
+      <c r="D113" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="J113" s="12" t="n">
+        <v>232.57</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>1627.96</v>
+      </c>
+      <c r="L113" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B114" s="12" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="C114" s="12" t="n">
+        <v>129.75</v>
+      </c>
+      <c r="D114" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I114" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="J114" s="12" t="n">
+        <v>242.48</v>
+      </c>
+      <c r="K114" s="12" t="n">
+        <v>1697.39</v>
+      </c>
+      <c r="L114" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B115" s="12" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="C115" s="12" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I115" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="J115" s="12" t="n">
+        <v>252.82</v>
+      </c>
+      <c r="K115" s="12" t="n">
+        <v>1769.77</v>
+      </c>
+      <c r="L115" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B116" s="12" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="C116" s="12" t="n">
+        <v>123.04</v>
+      </c>
+      <c r="D116" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I116" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="J116" s="12" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="K116" s="12" t="n">
+        <v>1845.23</v>
+      </c>
+      <c r="L116" s="13" t="n">
         <v>7</v>
       </c>
     </row>

--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="루나시트 VR일지" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현재 30단계 가이드" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -107,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,6 +154,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -233,7 +251,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -244,7 +262,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>루나시트 VR 5.0 총자산 및 목표선 추이</a:t>
+              <a:t>루나시트 VR 5.0 자산 및 평가금 추이</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -276,12 +294,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$82</f>
+              <f>'루나시트 VR일지'!$B$8:$B$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$E$8:$E$82</f>
+              <f>'루나시트 VR일지'!$E$8:$E$83</f>
             </numRef>
           </val>
         </ser>
@@ -308,12 +326,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$82</f>
+              <f>'루나시트 VR일지'!$B$8:$B$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$F$8:$F$82</f>
+              <f>'루나시트 VR일지'!$F$8:$F$83</f>
             </numRef>
           </val>
         </ser>
@@ -340,12 +358,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$82</f>
+              <f>'루나시트 VR일지'!$B$8:$B$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$G$8:$G$82</f>
+              <f>'루나시트 VR일지'!$G$8:$G$83</f>
             </numRef>
           </val>
         </ser>
@@ -382,6 +400,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="25000"/>
+          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -400,13 +420,250 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <majorUnit val="5000"/>
+      </valAx>
+      <dTable>
+        <showHorzBorder val="1"/>
+        <showVertBorder val="1"/>
+        <showOutline val="1"/>
+        <showKeys val="1"/>
+      </dTable>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="11"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>루나시트 VR 5.0 매수/매도 진단 차트 (주식평가금 vs V min / V / V max)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'루나시트 VR일지'!Q7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'루나시트 VR일지'!$B$8:$B$83</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'루나시트 VR일지'!$Q$8:$Q$83</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'루나시트 VR일지'!R7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'루나시트 VR일지'!$B$8:$B$83</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'루나시트 VR일지'!$R$8:$R$83</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'루나시트 VR일지'!S7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'루나시트 VR일지'!$B$8:$B$83</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'루나시트 VR일지'!$S$8:$S$83</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'루나시트 VR일지'!T7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'루나시트 VR일지'!$B$8:$B$83</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'루나시트 VR일지'!$T$8:$T$83</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>일자</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="25000"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>금액 ($)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <majorUnit val="5000"/>
       </valAx>
+      <dTable>
+        <showHorzBorder val="1"/>
+        <showVertBorder val="1"/>
+        <showOutline val="1"/>
+        <showKeys val="1"/>
+      </dTable>
     </plotArea>
     <legend>
-      <legendPos val="t"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -423,7 +680,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="4320000"/>
+    <ext cx="6480000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -433,6 +690,28 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -730,25 +1009,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:T116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -798,26 +1081,26 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="3" t="n">
-        <v>20911.43</v>
+        <v>21814.28</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>15684.3</v>
+        <v>13204.77</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5227.130000000001</v>
+        <v>8609.509999999998</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4934.43120675</v>
+        <v>17216.79</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4659.543908366188</v>
+        <v>15366.07985</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6304.088817201312</v>
+        <v>20789.40215</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -904,12 +1187,32 @@
           <t>매매필요금액($)</t>
         </is>
       </c>
+      <c r="Q7" s="19" t="inlineStr">
+        <is>
+          <t>주식평가금($)</t>
+        </is>
+      </c>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>하단선(V min)</t>
+        </is>
+      </c>
+      <c r="S7" s="19" t="inlineStr">
+        <is>
+          <t>기준목표선V</t>
+        </is>
+      </c>
+      <c r="T7" s="19" t="inlineStr">
+        <is>
+          <t>상단선(V max)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
@@ -917,7 +1220,7 @@
       <c r="C8" s="6" t="n">
         <v>70.87</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="22" t="n">
         <v>200</v>
       </c>
       <c r="E8" s="6" t="n">
@@ -935,7 +1238,7 @@
       <c r="I8" s="8" t="n">
         <v>0.2161</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>/10</t>
         </is>
@@ -952,7 +1255,7 @@
       <c r="N8" s="6" t="n">
         <v>23526.95</v>
       </c>
-      <c r="O8" s="9" t="inlineStr">
+      <c r="O8" s="23" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -960,14 +1263,24 @@
       <c r="P8" s="6" t="n">
         <v>3981.13</v>
       </c>
+      <c r="Q8" s="24" t="n">
+        <v>13991.69</v>
+      </c>
+      <c r="R8" s="24" t="n">
+        <v>15057.25</v>
+      </c>
+      <c r="S8" s="24" t="n">
+        <v>18423.45</v>
+      </c>
+      <c r="T8" s="24" t="n">
+        <v>23526.95</v>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>1회차 (5/14일)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
@@ -975,7 +1288,7 @@
       <c r="C9" s="6" t="n">
         <v>70.76000000000001</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="22" t="n">
         <v>213</v>
       </c>
       <c r="E9" s="6" t="n">
@@ -993,7 +1306,7 @@
       <c r="I9" s="8" t="n">
         <v>0.2711</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>/10</t>
         </is>
@@ -1010,7 +1323,7 @@
       <c r="N9" s="6" t="n">
         <v>23653.75</v>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="O9" s="23" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -1018,14 +1331,24 @@
       <c r="P9" s="6" t="n">
         <v>4106.02</v>
       </c>
+      <c r="Q9" s="24" t="n">
+        <v>14816.98</v>
+      </c>
+      <c r="R9" s="24" t="n">
+        <v>15138.4</v>
+      </c>
+      <c r="S9" s="24" t="n">
+        <v>18423.45</v>
+      </c>
+      <c r="T9" s="24" t="n">
+        <v>23653.75</v>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2회차 (1/14일)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="A10" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -1033,7 +1356,7 @@
       <c r="C10" s="6" t="n">
         <v>70.76000000000001</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="22" t="n">
         <v>213</v>
       </c>
       <c r="E10" s="6" t="n">
@@ -1051,7 +1374,7 @@
       <c r="I10" s="8" t="n">
         <v>0.7089</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>/10</t>
         </is>
@@ -1068,13 +1391,25 @@
       <c r="N10" s="6" t="n">
         <v>5431.37</v>
       </c>
-      <c r="O10" s="18" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="P10" s="6" t="n">
         <v>10101.87</v>
+      </c>
+      <c r="Q10" s="24" t="n">
+        <v>14824.8</v>
+      </c>
+      <c r="R10" s="24" t="n">
+        <v>4014.49</v>
+      </c>
+      <c r="S10" s="24" t="n">
+        <v>4389.77</v>
+      </c>
+      <c r="T10" s="24" t="n">
+        <v>5431.37</v>
       </c>
     </row>
     <row r="11">
@@ -2052,6 +2387,18 @@
       <c r="P45" s="6" t="n">
         <v>10408.38</v>
       </c>
+      <c r="Q45" s="24" t="n">
+        <v>14870.71</v>
+      </c>
+      <c r="R45" s="24" t="n">
+        <v>3792.98</v>
+      </c>
+      <c r="S45" s="24" t="n">
+        <v>4389.77</v>
+      </c>
+      <c r="T45" s="24" t="n">
+        <v>5131.68</v>
+      </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -2110,6 +2457,18 @@
       <c r="P46" s="6" t="n">
         <v>9500.77</v>
       </c>
+      <c r="Q46" s="24" t="n">
+        <v>14448.79</v>
+      </c>
+      <c r="R46" s="24" t="n">
+        <v>4205.82</v>
+      </c>
+      <c r="S46" s="24" t="n">
+        <v>4389.77</v>
+      </c>
+      <c r="T46" s="24" t="n">
+        <v>5690.23</v>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -2167,6 +2526,18 @@
       </c>
       <c r="P47" s="6" t="n">
         <v>9978.77</v>
+      </c>
+      <c r="Q47" s="24" t="n">
+        <v>14913.2</v>
+      </c>
+      <c r="R47" s="24" t="n">
+        <v>4194.27</v>
+      </c>
+      <c r="S47" s="24" t="n">
+        <v>4389.77</v>
+      </c>
+      <c r="T47" s="24" t="n">
+        <v>5674.6</v>
       </c>
     </row>
     <row r="48">
@@ -3144,8 +3515,87 @@
       <c r="P82" s="6" t="n">
         <v>10202.48</v>
       </c>
-    </row>
-    <row r="83"/>
+      <c r="Q82" s="24" t="n">
+        <v>15684.3</v>
+      </c>
+      <c r="R82" s="24" t="n">
+        <v>4659.54</v>
+      </c>
+      <c r="S82" s="24" t="n">
+        <v>4934.43</v>
+      </c>
+      <c r="T82" s="24" t="n">
+        <v>6304.09</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>76</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>71</v>
+      </c>
+      <c r="D83" t="n">
+        <v>167</v>
+      </c>
+      <c r="E83" t="n">
+        <v>13204.77</v>
+      </c>
+      <c r="F83" t="n">
+        <v>8609.51</v>
+      </c>
+      <c r="G83" t="n">
+        <v>21814.28</v>
+      </c>
+      <c r="H83" t="n">
+        <v>17216.79</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>/10</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L83" t="n">
+        <v>18077.74</v>
+      </c>
+      <c r="M83" t="n">
+        <v>15366.08</v>
+      </c>
+      <c r="N83" t="n">
+        <v>20789.4</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>4872.97</v>
+      </c>
+      <c r="Q83" s="24" t="n">
+        <v>13204.77</v>
+      </c>
+      <c r="R83" s="24" t="n">
+        <v>15366.08</v>
+      </c>
+      <c r="S83" s="24" t="n">
+        <v>17216.79</v>
+      </c>
+      <c r="T83" s="24" t="n">
+        <v>20789.4</v>
+      </c>
+    </row>
     <row r="84"/>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -3985,4 +4435,871 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🎯 VR 5.0 현재 30단계 매수/매도 그물망 가이드( 26.09.28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>🟢 [매수 30단계 차등가이드]</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>🔴 [매도 30단계 차등가이드]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>회차</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>지정가($)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>할당금액($)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>수량(주)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>회차</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>지정가($)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>할당금액($)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>수량(주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>156.52</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>80.61</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>403.04</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>155.21</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>81.52</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>407.59</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>153.89</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>82.44</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>412.18</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>76.29000000000001</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>152.58</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>416.83</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>75.63</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>151.26</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>84.31</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>421.53</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>74.97</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>149.95</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>85.26000000000001</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>426.29</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>148.63</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>73.66</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>147.32</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>87.19</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>435.96</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>440.88</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>144.69</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>445.85</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>71.69</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>143.37</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>450.88</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>71.03</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>142.06</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>91.19</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>455.96</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>140.74</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>92.22</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>461.11</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>139.43</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>466.31</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>69.06</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>138.11</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>94.31</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>471.57</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>136.79</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>476.88</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>135.48</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>482.26</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>67.08</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>134.16</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>487.7</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>66.42</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>132.85</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>493.2</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>131.53</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>498.77</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>130.22</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>100.88</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>504.39</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>102.02</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>510.08</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>63.79</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>127.59</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>103.17</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>515.83</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>63.14</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>126.27</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>104.33</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>521.65</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>124.96</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>105.51</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>527.54</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>123.64</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>533.49</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>122.33</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>539.5</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>121.01</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>109.12</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>545.59</v>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>551.74</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>118.38</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>111.59</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>557.96</v>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -346,6 +346,10 @@
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -467,12 +471,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$12</f>
+              <f>'루나시트 VR일지'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$E$8:$E$12</f>
+              <f>'루나시트 VR일지'!$E$8:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -499,12 +503,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$12</f>
+              <f>'루나시트 VR일지'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$F$8:$F$12</f>
+              <f>'루나시트 VR일지'!$F$8:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -531,12 +535,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$12</f>
+              <f>'루나시트 VR일지'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$G$8:$G$12</f>
+              <f>'루나시트 VR일지'!$G$8:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -662,12 +666,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$12</f>
+              <f>'루나시트 VR일지'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$Q$8:$Q$12</f>
+              <f>'루나시트 VR일지'!$Q$8:$Q$13</f>
             </numRef>
           </val>
         </ser>
@@ -694,12 +698,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$12</f>
+              <f>'루나시트 VR일지'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$R$8:$R$12</f>
+              <f>'루나시트 VR일지'!$R$8:$R$13</f>
             </numRef>
           </val>
         </ser>
@@ -726,12 +730,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$12</f>
+              <f>'루나시트 VR일지'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$S$8:$S$12</f>
+              <f>'루나시트 VR일지'!$S$8:$S$13</f>
             </numRef>
           </val>
         </ser>
@@ -758,12 +762,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$12</f>
+              <f>'루나시트 VR일지'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$T$8:$T$12</f>
+              <f>'루나시트 VR일지'!$T$8:$T$13</f>
             </numRef>
           </val>
         </ser>
@@ -1187,10 +1191,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="7"/>
+    <col width="21" customWidth="1" min="6" max="7"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="11"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -1254,26 +1258,26 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="32" t="n">
-        <v>22443.92</v>
+        <v>21516.87</v>
       </c>
       <c r="C4" s="32" t="n">
-        <v>17216.79</v>
+        <v>12907.36</v>
       </c>
       <c r="D4" s="32" t="n">
-        <v>5227.130000000001</v>
+        <v>8609.509999999998</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>17216.79</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>15078.57755</v>
+        <v>15366.07985</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>20400.42845</v>
+        <v>20789.40215</v>
       </c>
       <c r="H4" s="32" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1721,15 +1725,73 @@
         <v>20400.43</v>
       </c>
     </row>
-    <row r="13" ht="21.95" customHeight="1">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="43" t="n"/>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="43" t="n"/>
-      <c r="K13" s="43" t="n"/>
-      <c r="L13" s="9" t="n"/>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="n">
+        <v>71</v>
+      </c>
+      <c r="D13" s="38" t="n">
+        <v>167</v>
+      </c>
+      <c r="E13" s="37" t="n">
+        <v>12907.36</v>
+      </c>
+      <c r="F13" s="37" t="n">
+        <v>8609.51</v>
+      </c>
+      <c r="G13" s="37" t="n">
+        <v>21516.87</v>
+      </c>
+      <c r="H13" s="37" t="n">
+        <v>17216.79</v>
+      </c>
+      <c r="I13" s="39" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="J13" s="36" t="inlineStr">
+        <is>
+          <t>/10</t>
+        </is>
+      </c>
+      <c r="K13" s="39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L13" s="37" t="n">
+        <v>18077.74</v>
+      </c>
+      <c r="M13" s="37" t="n">
+        <v>15366.08</v>
+      </c>
+      <c r="N13" s="37" t="n">
+        <v>20789.4</v>
+      </c>
+      <c r="O13" s="50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P13" s="37" t="n">
+        <v>5170.38</v>
+      </c>
+      <c r="Q13" s="51" t="n">
+        <v>12907.36</v>
+      </c>
+      <c r="R13" s="51" t="n">
+        <v>15366.08</v>
+      </c>
+      <c r="S13" s="51" t="n">
+        <v>17216.79</v>
+      </c>
+      <c r="T13" s="51" t="n">
+        <v>20789.4</v>
+      </c>
     </row>
     <row r="14" ht="21.95" customHeight="1">
       <c r="A14" s="7" t="n"/>
@@ -2779,7 +2841,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="30" t="inlineStr">
         <is>
-          <t>🎯 VR 5.0 현재 30단계 매수/매도 그물망 가이드( 26.09.23)</t>
+          <t>🎯 VR 5.0 현재 30단계 매수/매도 그물망 가이드( 26.09.28)</t>
         </is>
       </c>
     </row>
@@ -2843,25 +2905,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="48" t="n">
-        <v>80.16</v>
+        <v>76.5</v>
       </c>
       <c r="C5" s="48" t="n">
-        <v>80.16</v>
+        <v>152.99</v>
       </c>
       <c r="D5" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="47" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="48" t="n">
-        <v>82.56</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H5" s="48" t="n">
-        <v>577.91</v>
+        <v>393.95</v>
       </c>
       <c r="I5" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2869,25 +2931,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="48" t="n">
-        <v>79.48</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="C6" s="48" t="n">
-        <v>79.48</v>
+        <v>151.71</v>
       </c>
       <c r="D6" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>83.48999999999999</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H6" s="48" t="n">
-        <v>584.4299999999999</v>
+        <v>398.39</v>
       </c>
       <c r="I6" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2895,25 +2957,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="48" t="n">
-        <v>78.81</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="C7" s="48" t="n">
-        <v>78.81</v>
+        <v>150.42</v>
       </c>
       <c r="D7" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="47" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="48" t="n">
-        <v>84.43000000000001</v>
+        <v>80.58</v>
       </c>
       <c r="H7" s="48" t="n">
-        <v>591.02</v>
+        <v>402.89</v>
       </c>
       <c r="I7" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2921,25 +2983,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="48" t="n">
-        <v>78.14</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="C8" s="48" t="n">
-        <v>78.14</v>
+        <v>149.14</v>
       </c>
       <c r="D8" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="48" t="n">
-        <v>85.38</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="H8" s="48" t="n">
-        <v>597.6900000000001</v>
+        <v>407.43</v>
       </c>
       <c r="I8" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -2947,25 +3009,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="48" t="n">
-        <v>77.45999999999999</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="C9" s="48" t="n">
-        <v>77.45999999999999</v>
+        <v>147.85</v>
       </c>
       <c r="D9" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="47" t="n">
         <v>5</v>
       </c>
       <c r="G9" s="48" t="n">
-        <v>86.34999999999999</v>
+        <v>82.41</v>
       </c>
       <c r="H9" s="48" t="n">
-        <v>604.4299999999999</v>
+        <v>412.03</v>
       </c>
       <c r="I9" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -2973,25 +3035,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="48" t="n">
-        <v>76.79000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="C10" s="48" t="n">
-        <v>76.79000000000001</v>
+        <v>146.57</v>
       </c>
       <c r="D10" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="48" t="n">
-        <v>87.31999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="H10" s="48" t="n">
-        <v>611.25</v>
+        <v>416.67</v>
       </c>
       <c r="I10" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -2999,25 +3061,25 @@
         <v>7</v>
       </c>
       <c r="B11" s="48" t="n">
-        <v>76.11</v>
+        <v>72.64</v>
       </c>
       <c r="C11" s="48" t="n">
-        <v>76.11</v>
+        <v>145.28</v>
       </c>
       <c r="D11" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="47" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="48" t="n">
-        <v>88.31</v>
+        <v>84.27</v>
       </c>
       <c r="H11" s="48" t="n">
-        <v>618.14</v>
+        <v>421.37</v>
       </c>
       <c r="I11" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -3025,25 +3087,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="48" t="n">
-        <v>75.44</v>
+        <v>72</v>
       </c>
       <c r="C12" s="48" t="n">
-        <v>75.44</v>
+        <v>143.99</v>
       </c>
       <c r="D12" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="G12" s="48" t="n">
-        <v>89.3</v>
+        <v>85.23</v>
       </c>
       <c r="H12" s="48" t="n">
-        <v>625.11</v>
+        <v>426.13</v>
       </c>
       <c r="I12" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -3051,25 +3113,25 @@
         <v>9</v>
       </c>
       <c r="B13" s="48" t="n">
-        <v>74.77</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="C13" s="48" t="n">
-        <v>74.77</v>
+        <v>142.71</v>
       </c>
       <c r="D13" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="47" t="n">
         <v>9</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>90.31</v>
+        <v>86.19</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>632.16</v>
+        <v>430.93</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3077,25 +3139,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="48" t="n">
-        <v>74.09</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="C14" s="48" t="n">
-        <v>74.09</v>
+        <v>141.42</v>
       </c>
       <c r="D14" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="G14" s="48" t="n">
-        <v>91.33</v>
+        <v>87.16</v>
       </c>
       <c r="H14" s="48" t="n">
-        <v>639.3</v>
+        <v>435.79</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -3103,25 +3165,25 @@
         <v>11</v>
       </c>
       <c r="B15" s="48" t="n">
-        <v>73.42</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="C15" s="48" t="n">
-        <v>73.42</v>
+        <v>140.14</v>
       </c>
       <c r="D15" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="47" t="n">
         <v>11</v>
       </c>
       <c r="G15" s="48" t="n">
-        <v>92.36</v>
+        <v>88.14</v>
       </c>
       <c r="H15" s="48" t="n">
-        <v>646.51</v>
+        <v>440.71</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -3129,25 +3191,25 @@
         <v>12</v>
       </c>
       <c r="B16" s="48" t="n">
-        <v>72.75</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C16" s="48" t="n">
-        <v>72.75</v>
+        <v>138.85</v>
       </c>
       <c r="D16" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="47" t="n">
         <v>12</v>
       </c>
       <c r="G16" s="48" t="n">
-        <v>93.40000000000001</v>
+        <v>89.14</v>
       </c>
       <c r="H16" s="48" t="n">
-        <v>653.8</v>
+        <v>445.68</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -3155,25 +3217,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="48" t="n">
-        <v>72.06999999999999</v>
+        <v>68.78</v>
       </c>
       <c r="C17" s="48" t="n">
-        <v>72.06999999999999</v>
+        <v>137.57</v>
       </c>
       <c r="D17" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="47" t="n">
         <v>13</v>
       </c>
       <c r="G17" s="48" t="n">
-        <v>94.45</v>
+        <v>90.14</v>
       </c>
       <c r="H17" s="48" t="n">
-        <v>661.17</v>
+        <v>450.71</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -3181,25 +3243,25 @@
         <v>14</v>
       </c>
       <c r="B18" s="48" t="n">
-        <v>71.40000000000001</v>
+        <v>68.14</v>
       </c>
       <c r="C18" s="48" t="n">
-        <v>71.40000000000001</v>
+        <v>136.28</v>
       </c>
       <c r="D18" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="47" t="n">
         <v>14</v>
       </c>
       <c r="G18" s="48" t="n">
-        <v>95.52</v>
+        <v>91.16</v>
       </c>
       <c r="H18" s="48" t="n">
-        <v>668.63</v>
+        <v>455.79</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -3207,25 +3269,25 @@
         <v>15</v>
       </c>
       <c r="B19" s="48" t="n">
-        <v>70.73</v>
+        <v>67.5</v>
       </c>
       <c r="C19" s="48" t="n">
-        <v>70.73</v>
+        <v>135</v>
       </c>
       <c r="D19" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="47" t="n">
         <v>15</v>
       </c>
       <c r="G19" s="48" t="n">
-        <v>96.59999999999999</v>
+        <v>92.19</v>
       </c>
       <c r="H19" s="48" t="n">
-        <v>676.17</v>
+        <v>460.93</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -3233,25 +3295,25 @@
         <v>16</v>
       </c>
       <c r="B20" s="48" t="n">
-        <v>70.05</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C20" s="48" t="n">
-        <v>70.05</v>
+        <v>133.71</v>
       </c>
       <c r="D20" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="47" t="n">
         <v>16</v>
       </c>
       <c r="G20" s="48" t="n">
-        <v>97.69</v>
+        <v>93.23</v>
       </c>
       <c r="H20" s="48" t="n">
-        <v>683.8</v>
+        <v>466.13</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -3259,25 +3321,25 @@
         <v>17</v>
       </c>
       <c r="B21" s="48" t="n">
-        <v>69.38</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="C21" s="48" t="n">
-        <v>69.38</v>
+        <v>132.42</v>
       </c>
       <c r="D21" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="47" t="n">
         <v>17</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>98.79000000000001</v>
+        <v>94.28</v>
       </c>
       <c r="H21" s="48" t="n">
-        <v>691.51</v>
+        <v>471.39</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -3285,25 +3347,25 @@
         <v>18</v>
       </c>
       <c r="B22" s="48" t="n">
-        <v>68.70999999999999</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="C22" s="48" t="n">
-        <v>68.70999999999999</v>
+        <v>131.14</v>
       </c>
       <c r="D22" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="47" t="n">
         <v>18</v>
       </c>
       <c r="G22" s="48" t="n">
-        <v>99.90000000000001</v>
+        <v>95.34</v>
       </c>
       <c r="H22" s="48" t="n">
-        <v>699.3099999999999</v>
+        <v>476.7</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -3311,25 +3373,25 @@
         <v>19</v>
       </c>
       <c r="B23" s="48" t="n">
-        <v>68.03</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="C23" s="48" t="n">
-        <v>68.03</v>
+        <v>129.85</v>
       </c>
       <c r="D23" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="47" t="n">
         <v>19</v>
       </c>
       <c r="G23" s="48" t="n">
-        <v>101.03</v>
+        <v>96.42</v>
       </c>
       <c r="H23" s="48" t="n">
-        <v>707.2</v>
+        <v>482.08</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -3337,25 +3399,25 @@
         <v>20</v>
       </c>
       <c r="B24" s="48" t="n">
-        <v>67.36</v>
+        <v>64.28</v>
       </c>
       <c r="C24" s="48" t="n">
-        <v>67.36</v>
+        <v>128.57</v>
       </c>
       <c r="D24" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="47" t="n">
         <v>20</v>
       </c>
       <c r="G24" s="48" t="n">
-        <v>102.17</v>
+        <v>97.5</v>
       </c>
       <c r="H24" s="48" t="n">
-        <v>715.17</v>
+        <v>487.52</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -3363,25 +3425,25 @@
         <v>21</v>
       </c>
       <c r="B25" s="48" t="n">
-        <v>66.68000000000001</v>
+        <v>63.64</v>
       </c>
       <c r="C25" s="48" t="n">
-        <v>66.68000000000001</v>
+        <v>127.28</v>
       </c>
       <c r="D25" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="47" t="n">
         <v>21</v>
       </c>
       <c r="G25" s="48" t="n">
-        <v>103.32</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H25" s="48" t="n">
-        <v>723.24</v>
+        <v>493.02</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -3389,25 +3451,25 @@
         <v>22</v>
       </c>
       <c r="B26" s="48" t="n">
-        <v>66.01000000000001</v>
+        <v>63</v>
       </c>
       <c r="C26" s="48" t="n">
-        <v>66.01000000000001</v>
+        <v>126</v>
       </c>
       <c r="D26" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="47" t="n">
         <v>22</v>
       </c>
       <c r="G26" s="48" t="n">
-        <v>104.49</v>
+        <v>99.72</v>
       </c>
       <c r="H26" s="48" t="n">
-        <v>731.4</v>
+        <v>498.58</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -3415,25 +3477,25 @@
         <v>23</v>
       </c>
       <c r="B27" s="48" t="n">
-        <v>65.34</v>
+        <v>62.35</v>
       </c>
       <c r="C27" s="48" t="n">
-        <v>65.34</v>
+        <v>124.71</v>
       </c>
       <c r="D27" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="47" t="n">
         <v>23</v>
       </c>
       <c r="G27" s="48" t="n">
-        <v>105.66</v>
+        <v>100.84</v>
       </c>
       <c r="H27" s="48" t="n">
-        <v>739.65</v>
+        <v>504.2</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -3441,25 +3503,25 @@
         <v>24</v>
       </c>
       <c r="B28" s="48" t="n">
-        <v>64.66</v>
+        <v>61.71</v>
       </c>
       <c r="C28" s="48" t="n">
-        <v>64.66</v>
+        <v>123.42</v>
       </c>
       <c r="D28" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="47" t="n">
         <v>24</v>
       </c>
       <c r="G28" s="48" t="n">
-        <v>106.86</v>
+        <v>101.98</v>
       </c>
       <c r="H28" s="48" t="n">
-        <v>747.99</v>
+        <v>509.89</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -3467,25 +3529,25 @@
         <v>25</v>
       </c>
       <c r="B29" s="48" t="n">
-        <v>63.99</v>
+        <v>61.07</v>
       </c>
       <c r="C29" s="48" t="n">
-        <v>63.99</v>
+        <v>122.14</v>
       </c>
       <c r="D29" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="47" t="n">
         <v>25</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>108.06</v>
+        <v>103.13</v>
       </c>
       <c r="H29" s="48" t="n">
-        <v>756.42</v>
+        <v>515.64</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -3493,25 +3555,25 @@
         <v>26</v>
       </c>
       <c r="B30" s="48" t="n">
-        <v>63.32</v>
+        <v>60.43</v>
       </c>
       <c r="C30" s="48" t="n">
-        <v>63.32</v>
+        <v>120.85</v>
       </c>
       <c r="D30" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="47" t="n">
         <v>26</v>
       </c>
       <c r="G30" s="48" t="n">
-        <v>109.28</v>
+        <v>104.29</v>
       </c>
       <c r="H30" s="48" t="n">
-        <v>764.96</v>
+        <v>521.45</v>
       </c>
       <c r="I30" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -3519,25 +3581,25 @@
         <v>27</v>
       </c>
       <c r="B31" s="48" t="n">
-        <v>62.64</v>
+        <v>59.78</v>
       </c>
       <c r="C31" s="48" t="n">
-        <v>62.64</v>
+        <v>119.57</v>
       </c>
       <c r="D31" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="47" t="n">
         <v>27</v>
       </c>
       <c r="G31" s="48" t="n">
-        <v>110.51</v>
+        <v>105.47</v>
       </c>
       <c r="H31" s="48" t="n">
-        <v>773.58</v>
+        <v>527.33</v>
       </c>
       <c r="I31" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -3545,25 +3607,25 @@
         <v>28</v>
       </c>
       <c r="B32" s="48" t="n">
-        <v>61.97</v>
+        <v>59.14</v>
       </c>
       <c r="C32" s="48" t="n">
-        <v>61.97</v>
+        <v>118.28</v>
       </c>
       <c r="D32" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="47" t="n">
         <v>28</v>
       </c>
       <c r="G32" s="48" t="n">
-        <v>111.76</v>
+        <v>106.66</v>
       </c>
       <c r="H32" s="48" t="n">
-        <v>782.3099999999999</v>
+        <v>533.28</v>
       </c>
       <c r="I32" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -3571,25 +3633,25 @@
         <v>29</v>
       </c>
       <c r="B33" s="48" t="n">
-        <v>61.3</v>
+        <v>58.5</v>
       </c>
       <c r="C33" s="48" t="n">
-        <v>61.3</v>
+        <v>117</v>
       </c>
       <c r="D33" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="47" t="n">
         <v>29</v>
       </c>
       <c r="G33" s="48" t="n">
-        <v>113.02</v>
+        <v>107.86</v>
       </c>
       <c r="H33" s="48" t="n">
-        <v>791.13</v>
+        <v>539.3</v>
       </c>
       <c r="I33" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -3597,25 +3659,25 @@
         <v>30</v>
       </c>
       <c r="B34" s="48" t="n">
-        <v>60.62</v>
+        <v>57.86</v>
       </c>
       <c r="C34" s="48" t="n">
-        <v>60.62</v>
+        <v>115.71</v>
       </c>
       <c r="D34" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="47" t="n">
         <v>30</v>
       </c>
       <c r="G34" s="48" t="n">
-        <v>114.29</v>
+        <v>109.08</v>
       </c>
       <c r="H34" s="48" t="n">
-        <v>800.0599999999999</v>
+        <v>545.38</v>
       </c>
       <c r="I34" s="49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -471,12 +471,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$13</f>
+              <f>'루나시트 VR일지'!$B$8:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$E$8:$E$13</f>
+              <f>'루나시트 VR일지'!$E$8:$E$14</f>
             </numRef>
           </val>
         </ser>
@@ -503,12 +503,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$13</f>
+              <f>'루나시트 VR일지'!$B$8:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$F$8:$F$13</f>
+              <f>'루나시트 VR일지'!$F$8:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -535,12 +535,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$13</f>
+              <f>'루나시트 VR일지'!$B$8:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$G$8:$G$13</f>
+              <f>'루나시트 VR일지'!$G$8:$G$14</f>
             </numRef>
           </val>
         </ser>
@@ -666,12 +666,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$13</f>
+              <f>'루나시트 VR일지'!$B$8:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$Q$8:$Q$13</f>
+              <f>'루나시트 VR일지'!$Q$8:$Q$14</f>
             </numRef>
           </val>
         </ser>
@@ -698,12 +698,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$13</f>
+              <f>'루나시트 VR일지'!$B$8:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$R$8:$R$13</f>
+              <f>'루나시트 VR일지'!$R$8:$R$14</f>
             </numRef>
           </val>
         </ser>
@@ -730,12 +730,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$13</f>
+              <f>'루나시트 VR일지'!$B$8:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$S$8:$S$13</f>
+              <f>'루나시트 VR일지'!$S$8:$S$14</f>
             </numRef>
           </val>
         </ser>
@@ -762,12 +762,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$13</f>
+              <f>'루나시트 VR일지'!$B$8:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$T$8:$T$13</f>
+              <f>'루나시트 VR일지'!$T$8:$T$14</f>
             </numRef>
           </val>
         </ser>
@@ -1191,8 +1191,8 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="7"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -1258,22 +1258,22 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="32" t="n">
-        <v>21516.87</v>
+        <v>14018.3</v>
       </c>
       <c r="C4" s="32" t="n">
-        <v>12907.36</v>
+        <v>11167.93</v>
       </c>
       <c r="D4" s="32" t="n">
-        <v>8609.509999999998</v>
+        <v>2850.37</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>17216.79</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>15366.07985</v>
+        <v>14876.55295</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>20789.40215</v>
+        <v>20127.10105</v>
       </c>
       <c r="H4" s="32" t="inlineStr">
         <is>
@@ -1793,15 +1793,73 @@
         <v>20789.4</v>
       </c>
     </row>
-    <row r="14" ht="21.95" customHeight="1">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="43" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="43" t="n"/>
-      <c r="K14" s="43" t="n"/>
-      <c r="L14" s="9" t="n"/>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="D14" s="38" t="n">
+        <v>136</v>
+      </c>
+      <c r="E14" s="37" t="n">
+        <v>11167.93</v>
+      </c>
+      <c r="F14" s="37" t="n">
+        <v>2850.37</v>
+      </c>
+      <c r="G14" s="37" t="n">
+        <v>14018.3</v>
+      </c>
+      <c r="H14" s="37" t="n">
+        <v>17216.79</v>
+      </c>
+      <c r="I14" s="39" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="J14" s="36" t="inlineStr">
+        <is>
+          <t>/10</t>
+        </is>
+      </c>
+      <c r="K14" s="39" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="L14" s="37" t="n">
+        <v>17501.83</v>
+      </c>
+      <c r="M14" s="37" t="n">
+        <v>14876.55</v>
+      </c>
+      <c r="N14" s="37" t="n">
+        <v>20127.1</v>
+      </c>
+      <c r="O14" s="50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P14" s="37" t="n">
+        <v>2850.37</v>
+      </c>
+      <c r="Q14" s="51" t="n">
+        <v>11167.93</v>
+      </c>
+      <c r="R14" s="51" t="n">
+        <v>14876.55</v>
+      </c>
+      <c r="S14" s="51" t="n">
+        <v>17216.79</v>
+      </c>
+      <c r="T14" s="51" t="n">
+        <v>20127.1</v>
+      </c>
     </row>
     <row r="15" ht="21.95" customHeight="1">
       <c r="A15" s="7" t="n"/>
@@ -2841,7 +2899,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="30" t="inlineStr">
         <is>
-          <t>🎯 VR 5.0 현재 30단계 매수/매도 그물망 가이드( 26.09.28)</t>
+          <t>🎯 VR 5.0 현재 30단계 매수/매도 그물망 가이드( 26.10.05)</t>
         </is>
       </c>
     </row>
@@ -2905,25 +2963,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="48" t="n">
-        <v>76.5</v>
+        <v>81.25</v>
       </c>
       <c r="C5" s="48" t="n">
-        <v>152.99</v>
+        <v>81.25</v>
       </c>
       <c r="D5" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="47" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="48" t="n">
-        <v>78.79000000000001</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="H5" s="48" t="n">
-        <v>393.95</v>
+        <v>334.73</v>
       </c>
       <c r="I5" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2931,25 +2989,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="48" t="n">
-        <v>75.84999999999999</v>
+        <v>80.56</v>
       </c>
       <c r="C6" s="48" t="n">
-        <v>151.71</v>
+        <v>80.56</v>
       </c>
       <c r="D6" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>79.68000000000001</v>
+        <v>84.63</v>
       </c>
       <c r="H6" s="48" t="n">
-        <v>398.39</v>
+        <v>338.51</v>
       </c>
       <c r="I6" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2957,25 +3015,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="48" t="n">
-        <v>75.20999999999999</v>
+        <v>79.88</v>
       </c>
       <c r="C7" s="48" t="n">
-        <v>150.42</v>
+        <v>79.88</v>
       </c>
       <c r="D7" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="47" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="48" t="n">
-        <v>80.58</v>
+        <v>85.58</v>
       </c>
       <c r="H7" s="48" t="n">
-        <v>402.89</v>
+        <v>342.32</v>
       </c>
       <c r="I7" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2983,25 +3041,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="48" t="n">
-        <v>74.56999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="C8" s="48" t="n">
-        <v>149.14</v>
+        <v>79.2</v>
       </c>
       <c r="D8" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="48" t="n">
-        <v>81.48999999999999</v>
+        <v>86.55</v>
       </c>
       <c r="H8" s="48" t="n">
-        <v>407.43</v>
+        <v>346.18</v>
       </c>
       <c r="I8" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3009,25 +3067,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="48" t="n">
-        <v>73.93000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="C9" s="48" t="n">
-        <v>147.85</v>
+        <v>78.52</v>
       </c>
       <c r="D9" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="47" t="n">
         <v>5</v>
       </c>
       <c r="G9" s="48" t="n">
-        <v>82.41</v>
+        <v>87.52</v>
       </c>
       <c r="H9" s="48" t="n">
-        <v>412.03</v>
+        <v>350.09</v>
       </c>
       <c r="I9" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3035,25 +3093,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="48" t="n">
-        <v>73.28</v>
+        <v>77.83</v>
       </c>
       <c r="C10" s="48" t="n">
-        <v>146.57</v>
+        <v>77.83</v>
       </c>
       <c r="D10" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="48" t="n">
-        <v>83.33</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="H10" s="48" t="n">
-        <v>416.67</v>
+        <v>354.04</v>
       </c>
       <c r="I10" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -3061,25 +3119,25 @@
         <v>7</v>
       </c>
       <c r="B11" s="48" t="n">
-        <v>72.64</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="C11" s="48" t="n">
-        <v>145.28</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="D11" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="47" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="48" t="n">
-        <v>84.27</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="H11" s="48" t="n">
-        <v>421.37</v>
+        <v>358.03</v>
       </c>
       <c r="I11" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -3087,25 +3145,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="48" t="n">
-        <v>72</v>
+        <v>76.47</v>
       </c>
       <c r="C12" s="48" t="n">
-        <v>143.99</v>
+        <v>76.47</v>
       </c>
       <c r="D12" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="G12" s="48" t="n">
-        <v>85.23</v>
+        <v>90.52</v>
       </c>
       <c r="H12" s="48" t="n">
-        <v>426.13</v>
+        <v>362.07</v>
       </c>
       <c r="I12" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -3113,25 +3171,25 @@
         <v>9</v>
       </c>
       <c r="B13" s="48" t="n">
-        <v>71.34999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="C13" s="48" t="n">
-        <v>142.71</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="D13" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="47" t="n">
         <v>9</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>86.19</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>430.93</v>
+        <v>366.15</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -3139,25 +3197,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="48" t="n">
-        <v>70.70999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="C14" s="48" t="n">
-        <v>141.42</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D14" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="G14" s="48" t="n">
-        <v>87.16</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="H14" s="48" t="n">
-        <v>435.79</v>
+        <v>370.28</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -3165,25 +3223,25 @@
         <v>11</v>
       </c>
       <c r="B15" s="48" t="n">
-        <v>70.06999999999999</v>
+        <v>74.42</v>
       </c>
       <c r="C15" s="48" t="n">
-        <v>140.14</v>
+        <v>74.42</v>
       </c>
       <c r="D15" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="47" t="n">
         <v>11</v>
       </c>
       <c r="G15" s="48" t="n">
-        <v>88.14</v>
+        <v>93.61</v>
       </c>
       <c r="H15" s="48" t="n">
-        <v>440.71</v>
+        <v>374.46</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -3191,25 +3249,25 @@
         <v>12</v>
       </c>
       <c r="B16" s="48" t="n">
-        <v>69.43000000000001</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="C16" s="48" t="n">
-        <v>138.85</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="D16" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="47" t="n">
         <v>12</v>
       </c>
       <c r="G16" s="48" t="n">
-        <v>89.14</v>
+        <v>94.67</v>
       </c>
       <c r="H16" s="48" t="n">
-        <v>445.68</v>
+        <v>378.68</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -3217,25 +3275,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="48" t="n">
-        <v>68.78</v>
+        <v>73.05</v>
       </c>
       <c r="C17" s="48" t="n">
-        <v>137.57</v>
+        <v>73.05</v>
       </c>
       <c r="D17" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="47" t="n">
         <v>13</v>
       </c>
       <c r="G17" s="48" t="n">
-        <v>90.14</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="H17" s="48" t="n">
-        <v>450.71</v>
+        <v>382.95</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3243,25 +3301,25 @@
         <v>14</v>
       </c>
       <c r="B18" s="48" t="n">
-        <v>68.14</v>
+        <v>72.37</v>
       </c>
       <c r="C18" s="48" t="n">
-        <v>136.28</v>
+        <v>72.37</v>
       </c>
       <c r="D18" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="47" t="n">
         <v>14</v>
       </c>
       <c r="G18" s="48" t="n">
-        <v>91.16</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="H18" s="48" t="n">
-        <v>455.79</v>
+        <v>387.27</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -3269,25 +3327,25 @@
         <v>15</v>
       </c>
       <c r="B19" s="48" t="n">
-        <v>67.5</v>
+        <v>71.69</v>
       </c>
       <c r="C19" s="48" t="n">
-        <v>135</v>
+        <v>71.69</v>
       </c>
       <c r="D19" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="47" t="n">
         <v>15</v>
       </c>
       <c r="G19" s="48" t="n">
-        <v>92.19</v>
+        <v>97.91</v>
       </c>
       <c r="H19" s="48" t="n">
-        <v>460.93</v>
+        <v>391.64</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -3295,25 +3353,25 @@
         <v>16</v>
       </c>
       <c r="B20" s="48" t="n">
-        <v>66.84999999999999</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="C20" s="48" t="n">
-        <v>133.71</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="D20" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="47" t="n">
         <v>16</v>
       </c>
       <c r="G20" s="48" t="n">
-        <v>93.23</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="H20" s="48" t="n">
-        <v>466.13</v>
+        <v>396.06</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -3321,25 +3379,25 @@
         <v>17</v>
       </c>
       <c r="B21" s="48" t="n">
-        <v>66.20999999999999</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="C21" s="48" t="n">
-        <v>132.42</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="D21" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="47" t="n">
         <v>17</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>94.28</v>
+        <v>100.13</v>
       </c>
       <c r="H21" s="48" t="n">
-        <v>471.39</v>
+        <v>400.53</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -3347,25 +3405,25 @@
         <v>18</v>
       </c>
       <c r="B22" s="48" t="n">
-        <v>65.56999999999999</v>
+        <v>69.64</v>
       </c>
       <c r="C22" s="48" t="n">
-        <v>131.14</v>
+        <v>69.64</v>
       </c>
       <c r="D22" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="47" t="n">
         <v>18</v>
       </c>
       <c r="G22" s="48" t="n">
-        <v>95.34</v>
+        <v>101.26</v>
       </c>
       <c r="H22" s="48" t="n">
-        <v>476.7</v>
+        <v>405.04</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -3373,25 +3431,25 @@
         <v>19</v>
       </c>
       <c r="B23" s="48" t="n">
-        <v>64.93000000000001</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="C23" s="48" t="n">
-        <v>129.85</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="D23" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="47" t="n">
         <v>19</v>
       </c>
       <c r="G23" s="48" t="n">
-        <v>96.42</v>
+        <v>102.4</v>
       </c>
       <c r="H23" s="48" t="n">
-        <v>482.08</v>
+        <v>409.61</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -3399,25 +3457,25 @@
         <v>20</v>
       </c>
       <c r="B24" s="48" t="n">
-        <v>64.28</v>
+        <v>68.28</v>
       </c>
       <c r="C24" s="48" t="n">
-        <v>128.57</v>
+        <v>68.28</v>
       </c>
       <c r="D24" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="47" t="n">
         <v>20</v>
       </c>
       <c r="G24" s="48" t="n">
-        <v>97.5</v>
+        <v>103.56</v>
       </c>
       <c r="H24" s="48" t="n">
-        <v>487.52</v>
+        <v>414.23</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -3425,25 +3483,25 @@
         <v>21</v>
       </c>
       <c r="B25" s="48" t="n">
-        <v>63.64</v>
+        <v>67.59</v>
       </c>
       <c r="C25" s="48" t="n">
-        <v>127.28</v>
+        <v>67.59</v>
       </c>
       <c r="D25" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="47" t="n">
         <v>21</v>
       </c>
       <c r="G25" s="48" t="n">
-        <v>98.59999999999999</v>
+        <v>104.73</v>
       </c>
       <c r="H25" s="48" t="n">
-        <v>493.02</v>
+        <v>418.9</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -3451,25 +3509,25 @@
         <v>22</v>
       </c>
       <c r="B26" s="48" t="n">
-        <v>63</v>
+        <v>66.91</v>
       </c>
       <c r="C26" s="48" t="n">
-        <v>126</v>
+        <v>66.91</v>
       </c>
       <c r="D26" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="47" t="n">
         <v>22</v>
       </c>
       <c r="G26" s="48" t="n">
-        <v>99.72</v>
+        <v>105.91</v>
       </c>
       <c r="H26" s="48" t="n">
-        <v>498.58</v>
+        <v>423.63</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -3477,25 +3535,25 @@
         <v>23</v>
       </c>
       <c r="B27" s="48" t="n">
-        <v>62.35</v>
+        <v>66.23</v>
       </c>
       <c r="C27" s="48" t="n">
-        <v>124.71</v>
+        <v>66.23</v>
       </c>
       <c r="D27" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="47" t="n">
         <v>23</v>
       </c>
       <c r="G27" s="48" t="n">
-        <v>100.84</v>
+        <v>107.1</v>
       </c>
       <c r="H27" s="48" t="n">
-        <v>504.2</v>
+        <v>428.41</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -3503,25 +3561,25 @@
         <v>24</v>
       </c>
       <c r="B28" s="48" t="n">
-        <v>61.71</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="C28" s="48" t="n">
-        <v>123.42</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="D28" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="47" t="n">
         <v>24</v>
       </c>
       <c r="G28" s="48" t="n">
-        <v>101.98</v>
+        <v>108.31</v>
       </c>
       <c r="H28" s="48" t="n">
-        <v>509.89</v>
+        <v>433.24</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -3529,25 +3587,25 @@
         <v>25</v>
       </c>
       <c r="B29" s="48" t="n">
-        <v>61.07</v>
+        <v>64.86</v>
       </c>
       <c r="C29" s="48" t="n">
-        <v>122.14</v>
+        <v>64.86</v>
       </c>
       <c r="D29" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="47" t="n">
         <v>25</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>103.13</v>
+        <v>109.53</v>
       </c>
       <c r="H29" s="48" t="n">
-        <v>515.64</v>
+        <v>438.12</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -3555,25 +3613,25 @@
         <v>26</v>
       </c>
       <c r="B30" s="48" t="n">
-        <v>60.43</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="C30" s="48" t="n">
-        <v>120.85</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="D30" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="47" t="n">
         <v>26</v>
       </c>
       <c r="G30" s="48" t="n">
-        <v>104.29</v>
+        <v>110.77</v>
       </c>
       <c r="H30" s="48" t="n">
-        <v>521.45</v>
+        <v>443.07</v>
       </c>
       <c r="I30" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -3581,25 +3639,25 @@
         <v>27</v>
       </c>
       <c r="B31" s="48" t="n">
-        <v>59.78</v>
+        <v>63.5</v>
       </c>
       <c r="C31" s="48" t="n">
-        <v>119.57</v>
+        <v>63.5</v>
       </c>
       <c r="D31" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="47" t="n">
         <v>27</v>
       </c>
       <c r="G31" s="48" t="n">
-        <v>105.47</v>
+        <v>112.02</v>
       </c>
       <c r="H31" s="48" t="n">
-        <v>527.33</v>
+        <v>448.06</v>
       </c>
       <c r="I31" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -3607,25 +3665,25 @@
         <v>28</v>
       </c>
       <c r="B32" s="48" t="n">
-        <v>59.14</v>
+        <v>62.81</v>
       </c>
       <c r="C32" s="48" t="n">
-        <v>118.28</v>
+        <v>62.81</v>
       </c>
       <c r="D32" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="47" t="n">
         <v>28</v>
       </c>
       <c r="G32" s="48" t="n">
-        <v>106.66</v>
+        <v>113.28</v>
       </c>
       <c r="H32" s="48" t="n">
-        <v>533.28</v>
+        <v>453.12</v>
       </c>
       <c r="I32" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -3633,25 +3691,25 @@
         <v>29</v>
       </c>
       <c r="B33" s="48" t="n">
-        <v>58.5</v>
+        <v>62.13</v>
       </c>
       <c r="C33" s="48" t="n">
-        <v>117</v>
+        <v>62.13</v>
       </c>
       <c r="D33" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="47" t="n">
         <v>29</v>
       </c>
       <c r="G33" s="48" t="n">
-        <v>107.86</v>
+        <v>114.56</v>
       </c>
       <c r="H33" s="48" t="n">
-        <v>539.3</v>
+        <v>458.23</v>
       </c>
       <c r="I33" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -3659,25 +3717,25 @@
         <v>30</v>
       </c>
       <c r="B34" s="48" t="n">
-        <v>57.86</v>
+        <v>61.45</v>
       </c>
       <c r="C34" s="48" t="n">
-        <v>115.71</v>
+        <v>61.45</v>
       </c>
       <c r="D34" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="47" t="n">
         <v>30</v>
       </c>
       <c r="G34" s="48" t="n">
-        <v>109.08</v>
+        <v>115.85</v>
       </c>
       <c r="H34" s="48" t="n">
-        <v>545.38</v>
+        <v>463.4</v>
       </c>
       <c r="I34" s="49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -471,12 +471,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$14</f>
+              <f>'루나시트 VR일지'!$B$8:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$E$8:$E$14</f>
+              <f>'루나시트 VR일지'!$E$8:$E$15</f>
             </numRef>
           </val>
         </ser>
@@ -503,12 +503,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$14</f>
+              <f>'루나시트 VR일지'!$B$8:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$F$8:$F$14</f>
+              <f>'루나시트 VR일지'!$F$8:$F$15</f>
             </numRef>
           </val>
         </ser>
@@ -535,12 +535,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$14</f>
+              <f>'루나시트 VR일지'!$B$8:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$G$8:$G$14</f>
+              <f>'루나시트 VR일지'!$G$8:$G$15</f>
             </numRef>
           </val>
         </ser>
@@ -666,12 +666,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$14</f>
+              <f>'루나시트 VR일지'!$B$8:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$Q$8:$Q$14</f>
+              <f>'루나시트 VR일지'!$Q$8:$Q$15</f>
             </numRef>
           </val>
         </ser>
@@ -698,12 +698,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$14</f>
+              <f>'루나시트 VR일지'!$B$8:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$R$8:$R$14</f>
+              <f>'루나시트 VR일지'!$R$8:$R$15</f>
             </numRef>
           </val>
         </ser>
@@ -730,12 +730,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$14</f>
+              <f>'루나시트 VR일지'!$B$8:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$S$8:$S$14</f>
+              <f>'루나시트 VR일지'!$S$8:$S$15</f>
             </numRef>
           </val>
         </ser>
@@ -762,12 +762,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$14</f>
+              <f>'루나시트 VR일지'!$B$8:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$T$8:$T$14</f>
+              <f>'루나시트 VR일지'!$T$8:$T$15</f>
             </numRef>
           </val>
         </ser>
@@ -1192,9 +1192,9 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="7"/>
+    <col width="14" customWidth="1" min="6" max="7"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="11"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -1258,22 +1258,22 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="32" t="n">
-        <v>14018.3</v>
+        <v>22398.28</v>
       </c>
       <c r="C4" s="32" t="n">
-        <v>11167.93</v>
+        <v>11180.25</v>
       </c>
       <c r="D4" s="32" t="n">
-        <v>2850.37</v>
+        <v>11218.03</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>17216.79</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>14876.55295</v>
+        <v>15587.80405</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>20127.10105</v>
+        <v>21089.38195</v>
       </c>
       <c r="H4" s="32" t="inlineStr">
         <is>
@@ -1861,15 +1861,73 @@
         <v>20127.1</v>
       </c>
     </row>
-    <row r="15" ht="21.95" customHeight="1">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="43" t="n"/>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="43" t="n"/>
-      <c r="K15" s="43" t="n"/>
-      <c r="L15" s="9" t="n"/>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="D15" s="38" t="n">
+        <v>136</v>
+      </c>
+      <c r="E15" s="37" t="n">
+        <v>11180.25</v>
+      </c>
+      <c r="F15" s="37" t="n">
+        <v>11218.03</v>
+      </c>
+      <c r="G15" s="37" t="n">
+        <v>22398.28</v>
+      </c>
+      <c r="H15" s="37" t="n">
+        <v>17216.79</v>
+      </c>
+      <c r="I15" s="39" t="n">
+        <v>0.6516</v>
+      </c>
+      <c r="J15" s="36" t="inlineStr">
+        <is>
+          <t>/10</t>
+        </is>
+      </c>
+      <c r="K15" s="39" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="L15" s="37" t="n">
+        <v>18338.59</v>
+      </c>
+      <c r="M15" s="37" t="n">
+        <v>15587.8</v>
+      </c>
+      <c r="N15" s="37" t="n">
+        <v>21089.38</v>
+      </c>
+      <c r="O15" s="50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P15" s="37" t="n">
+        <v>7158.34</v>
+      </c>
+      <c r="Q15" s="51" t="n">
+        <v>11180.25</v>
+      </c>
+      <c r="R15" s="51" t="n">
+        <v>15587.8</v>
+      </c>
+      <c r="S15" s="51" t="n">
+        <v>17216.79</v>
+      </c>
+      <c r="T15" s="51" t="n">
+        <v>21089.38</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -2899,7 +2957,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="30" t="inlineStr">
         <is>
-          <t>🎯 VR 5.0 현재 30단계 매수/매도 그물망 가이드( 26.10.05)</t>
+          <t>🎯 VR 5.0 현재 30단계 매수/매도 그물망 가이드( 26.10.12)</t>
         </is>
       </c>
     </row>
@@ -2963,22 +3021,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="48" t="n">
-        <v>81.25</v>
+        <v>81.34</v>
       </c>
       <c r="C5" s="48" t="n">
-        <v>81.25</v>
+        <v>244.01</v>
       </c>
       <c r="D5" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="47" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="48" t="n">
-        <v>83.68000000000001</v>
+        <v>83.77</v>
       </c>
       <c r="H5" s="48" t="n">
-        <v>334.73</v>
+        <v>335.1</v>
       </c>
       <c r="I5" s="49" t="n">
         <v>4</v>
@@ -2989,22 +3047,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="48" t="n">
-        <v>80.56</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="C6" s="48" t="n">
-        <v>80.56</v>
+        <v>241.96</v>
       </c>
       <c r="D6" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>84.63</v>
+        <v>84.72</v>
       </c>
       <c r="H6" s="48" t="n">
-        <v>338.51</v>
+        <v>338.88</v>
       </c>
       <c r="I6" s="49" t="n">
         <v>4</v>
@@ -3015,22 +3073,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="48" t="n">
-        <v>79.88</v>
+        <v>79.97</v>
       </c>
       <c r="C7" s="48" t="n">
-        <v>79.88</v>
+        <v>239.91</v>
       </c>
       <c r="D7" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="47" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="48" t="n">
-        <v>85.58</v>
+        <v>85.67</v>
       </c>
       <c r="H7" s="48" t="n">
-        <v>342.32</v>
+        <v>342.7</v>
       </c>
       <c r="I7" s="49" t="n">
         <v>4</v>
@@ -3041,22 +3099,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="48" t="n">
-        <v>79.2</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="C8" s="48" t="n">
-        <v>79.2</v>
+        <v>237.86</v>
       </c>
       <c r="D8" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="48" t="n">
-        <v>86.55</v>
+        <v>86.64</v>
       </c>
       <c r="H8" s="48" t="n">
-        <v>346.18</v>
+        <v>346.57</v>
       </c>
       <c r="I8" s="49" t="n">
         <v>4</v>
@@ -3067,22 +3125,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="48" t="n">
-        <v>78.52</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="C9" s="48" t="n">
-        <v>78.52</v>
+        <v>235.81</v>
       </c>
       <c r="D9" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="47" t="n">
         <v>5</v>
       </c>
       <c r="G9" s="48" t="n">
-        <v>87.52</v>
+        <v>87.62</v>
       </c>
       <c r="H9" s="48" t="n">
-        <v>350.09</v>
+        <v>350.47</v>
       </c>
       <c r="I9" s="49" t="n">
         <v>4</v>
@@ -3093,22 +3151,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="48" t="n">
-        <v>77.83</v>
+        <v>77.92</v>
       </c>
       <c r="C10" s="48" t="n">
-        <v>77.83</v>
+        <v>233.76</v>
       </c>
       <c r="D10" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="48" t="n">
-        <v>88.51000000000001</v>
+        <v>88.61</v>
       </c>
       <c r="H10" s="48" t="n">
-        <v>354.04</v>
+        <v>354.43</v>
       </c>
       <c r="I10" s="49" t="n">
         <v>4</v>
@@ -3119,22 +3177,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="48" t="n">
-        <v>77.15000000000001</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="C11" s="48" t="n">
-        <v>77.15000000000001</v>
+        <v>231.71</v>
       </c>
       <c r="D11" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="47" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="48" t="n">
-        <v>89.51000000000001</v>
+        <v>89.61</v>
       </c>
       <c r="H11" s="48" t="n">
-        <v>358.03</v>
+        <v>358.42</v>
       </c>
       <c r="I11" s="49" t="n">
         <v>4</v>
@@ -3145,22 +3203,22 @@
         <v>8</v>
       </c>
       <c r="B12" s="48" t="n">
-        <v>76.47</v>
+        <v>76.55</v>
       </c>
       <c r="C12" s="48" t="n">
-        <v>76.47</v>
+        <v>229.66</v>
       </c>
       <c r="D12" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="G12" s="48" t="n">
-        <v>90.52</v>
+        <v>90.62</v>
       </c>
       <c r="H12" s="48" t="n">
-        <v>362.07</v>
+        <v>362.47</v>
       </c>
       <c r="I12" s="49" t="n">
         <v>4</v>
@@ -3171,22 +3229,22 @@
         <v>9</v>
       </c>
       <c r="B13" s="48" t="n">
-        <v>75.79000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="C13" s="48" t="n">
-        <v>75.79000000000001</v>
+        <v>227.61</v>
       </c>
       <c r="D13" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="47" t="n">
         <v>9</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>91.54000000000001</v>
+        <v>91.64</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>366.15</v>
+        <v>366.56</v>
       </c>
       <c r="I13" s="49" t="n">
         <v>4</v>
@@ -3197,22 +3255,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="48" t="n">
-        <v>75.09999999999999</v>
+        <v>75.19</v>
       </c>
       <c r="C14" s="48" t="n">
-        <v>75.09999999999999</v>
+        <v>225.56</v>
       </c>
       <c r="D14" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="G14" s="48" t="n">
-        <v>92.56999999999999</v>
+        <v>92.67</v>
       </c>
       <c r="H14" s="48" t="n">
-        <v>370.28</v>
+        <v>370.69</v>
       </c>
       <c r="I14" s="49" t="n">
         <v>4</v>
@@ -3223,22 +3281,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="48" t="n">
-        <v>74.42</v>
+        <v>74.5</v>
       </c>
       <c r="C15" s="48" t="n">
-        <v>74.42</v>
+        <v>223.5</v>
       </c>
       <c r="D15" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="47" t="n">
         <v>11</v>
       </c>
       <c r="G15" s="48" t="n">
-        <v>93.61</v>
+        <v>93.72</v>
       </c>
       <c r="H15" s="48" t="n">
-        <v>374.46</v>
+        <v>374.87</v>
       </c>
       <c r="I15" s="49" t="n">
         <v>4</v>
@@ -3249,22 +3307,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="48" t="n">
-        <v>73.73999999999999</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="C16" s="48" t="n">
-        <v>73.73999999999999</v>
+        <v>221.45</v>
       </c>
       <c r="D16" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="47" t="n">
         <v>12</v>
       </c>
       <c r="G16" s="48" t="n">
-        <v>94.67</v>
+        <v>94.77</v>
       </c>
       <c r="H16" s="48" t="n">
-        <v>378.68</v>
+        <v>379.1</v>
       </c>
       <c r="I16" s="49" t="n">
         <v>4</v>
@@ -3275,22 +3333,22 @@
         <v>13</v>
       </c>
       <c r="B17" s="48" t="n">
-        <v>73.05</v>
+        <v>73.13</v>
       </c>
       <c r="C17" s="48" t="n">
-        <v>73.05</v>
+        <v>219.4</v>
       </c>
       <c r="D17" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="47" t="n">
         <v>13</v>
       </c>
       <c r="G17" s="48" t="n">
-        <v>95.73999999999999</v>
+        <v>95.84</v>
       </c>
       <c r="H17" s="48" t="n">
-        <v>382.95</v>
+        <v>383.37</v>
       </c>
       <c r="I17" s="49" t="n">
         <v>4</v>
@@ -3301,22 +3359,22 @@
         <v>14</v>
       </c>
       <c r="B18" s="48" t="n">
-        <v>72.37</v>
+        <v>72.45</v>
       </c>
       <c r="C18" s="48" t="n">
-        <v>72.37</v>
+        <v>217.35</v>
       </c>
       <c r="D18" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="47" t="n">
         <v>14</v>
       </c>
       <c r="G18" s="48" t="n">
-        <v>96.81999999999999</v>
+        <v>96.92</v>
       </c>
       <c r="H18" s="48" t="n">
-        <v>387.27</v>
+        <v>387.7</v>
       </c>
       <c r="I18" s="49" t="n">
         <v>4</v>
@@ -3327,22 +3385,22 @@
         <v>15</v>
       </c>
       <c r="B19" s="48" t="n">
-        <v>71.69</v>
+        <v>71.77</v>
       </c>
       <c r="C19" s="48" t="n">
-        <v>71.69</v>
+        <v>215.3</v>
       </c>
       <c r="D19" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="47" t="n">
         <v>15</v>
       </c>
       <c r="G19" s="48" t="n">
-        <v>97.91</v>
+        <v>98.02</v>
       </c>
       <c r="H19" s="48" t="n">
-        <v>391.64</v>
+        <v>392.07</v>
       </c>
       <c r="I19" s="49" t="n">
         <v>4</v>
@@ -3353,22 +3411,22 @@
         <v>16</v>
       </c>
       <c r="B20" s="48" t="n">
-        <v>71.01000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="C20" s="48" t="n">
-        <v>71.01000000000001</v>
+        <v>213.25</v>
       </c>
       <c r="D20" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" s="47" t="n">
         <v>16</v>
       </c>
       <c r="G20" s="48" t="n">
-        <v>99.01000000000001</v>
+        <v>99.12</v>
       </c>
       <c r="H20" s="48" t="n">
-        <v>396.06</v>
+        <v>396.49</v>
       </c>
       <c r="I20" s="49" t="n">
         <v>4</v>
@@ -3379,22 +3437,22 @@
         <v>17</v>
       </c>
       <c r="B21" s="48" t="n">
-        <v>70.31999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C21" s="48" t="n">
-        <v>70.31999999999999</v>
+        <v>211.2</v>
       </c>
       <c r="D21" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="47" t="n">
         <v>17</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>100.13</v>
+        <v>100.24</v>
       </c>
       <c r="H21" s="48" t="n">
-        <v>400.53</v>
+        <v>400.97</v>
       </c>
       <c r="I21" s="49" t="n">
         <v>4</v>
@@ -3405,22 +3463,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="48" t="n">
-        <v>69.64</v>
+        <v>69.72</v>
       </c>
       <c r="C22" s="48" t="n">
-        <v>69.64</v>
+        <v>209.15</v>
       </c>
       <c r="D22" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="47" t="n">
         <v>18</v>
       </c>
       <c r="G22" s="48" t="n">
-        <v>101.26</v>
+        <v>101.37</v>
       </c>
       <c r="H22" s="48" t="n">
-        <v>405.04</v>
+        <v>405.49</v>
       </c>
       <c r="I22" s="49" t="n">
         <v>4</v>
@@ -3431,22 +3489,22 @@
         <v>19</v>
       </c>
       <c r="B23" s="48" t="n">
-        <v>68.95999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="C23" s="48" t="n">
-        <v>68.95999999999999</v>
+        <v>207.1</v>
       </c>
       <c r="D23" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="47" t="n">
         <v>19</v>
       </c>
       <c r="G23" s="48" t="n">
-        <v>102.4</v>
+        <v>102.52</v>
       </c>
       <c r="H23" s="48" t="n">
-        <v>409.61</v>
+        <v>410.06</v>
       </c>
       <c r="I23" s="49" t="n">
         <v>4</v>
@@ -3457,22 +3515,22 @@
         <v>20</v>
       </c>
       <c r="B24" s="48" t="n">
-        <v>68.28</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="C24" s="48" t="n">
-        <v>68.28</v>
+        <v>205.05</v>
       </c>
       <c r="D24" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="47" t="n">
         <v>20</v>
       </c>
       <c r="G24" s="48" t="n">
-        <v>103.56</v>
+        <v>103.67</v>
       </c>
       <c r="H24" s="48" t="n">
-        <v>414.23</v>
+        <v>414.69</v>
       </c>
       <c r="I24" s="49" t="n">
         <v>4</v>
@@ -3483,22 +3541,22 @@
         <v>21</v>
       </c>
       <c r="B25" s="48" t="n">
-        <v>67.59</v>
+        <v>67.67</v>
       </c>
       <c r="C25" s="48" t="n">
-        <v>67.59</v>
+        <v>203</v>
       </c>
       <c r="D25" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="47" t="n">
         <v>21</v>
       </c>
       <c r="G25" s="48" t="n">
-        <v>104.73</v>
+        <v>104.84</v>
       </c>
       <c r="H25" s="48" t="n">
-        <v>418.9</v>
+        <v>419.36</v>
       </c>
       <c r="I25" s="49" t="n">
         <v>4</v>
@@ -3509,22 +3567,22 @@
         <v>22</v>
       </c>
       <c r="B26" s="48" t="n">
-        <v>66.91</v>
+        <v>66.98</v>
       </c>
       <c r="C26" s="48" t="n">
-        <v>66.91</v>
+        <v>200.95</v>
       </c>
       <c r="D26" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" s="47" t="n">
         <v>22</v>
       </c>
       <c r="G26" s="48" t="n">
-        <v>105.91</v>
+        <v>106.02</v>
       </c>
       <c r="H26" s="48" t="n">
-        <v>423.63</v>
+        <v>424.09</v>
       </c>
       <c r="I26" s="49" t="n">
         <v>4</v>
@@ -3535,22 +3593,22 @@
         <v>23</v>
       </c>
       <c r="B27" s="48" t="n">
-        <v>66.23</v>
+        <v>66.3</v>
       </c>
       <c r="C27" s="48" t="n">
-        <v>66.23</v>
+        <v>198.9</v>
       </c>
       <c r="D27" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" s="47" t="n">
         <v>23</v>
       </c>
       <c r="G27" s="48" t="n">
-        <v>107.1</v>
+        <v>107.22</v>
       </c>
       <c r="H27" s="48" t="n">
-        <v>428.41</v>
+        <v>428.88</v>
       </c>
       <c r="I27" s="49" t="n">
         <v>4</v>
@@ -3561,22 +3619,22 @@
         <v>24</v>
       </c>
       <c r="B28" s="48" t="n">
-        <v>65.54000000000001</v>
+        <v>65.62</v>
       </c>
       <c r="C28" s="48" t="n">
-        <v>65.54000000000001</v>
+        <v>196.85</v>
       </c>
       <c r="D28" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" s="47" t="n">
         <v>24</v>
       </c>
       <c r="G28" s="48" t="n">
-        <v>108.31</v>
+        <v>108.43</v>
       </c>
       <c r="H28" s="48" t="n">
-        <v>433.24</v>
+        <v>433.71</v>
       </c>
       <c r="I28" s="49" t="n">
         <v>4</v>
@@ -3587,22 +3645,22 @@
         <v>25</v>
       </c>
       <c r="B29" s="48" t="n">
-        <v>64.86</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="C29" s="48" t="n">
-        <v>64.86</v>
+        <v>194.8</v>
       </c>
       <c r="D29" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="47" t="n">
         <v>25</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>109.53</v>
+        <v>109.65</v>
       </c>
       <c r="H29" s="48" t="n">
-        <v>438.12</v>
+        <v>438.61</v>
       </c>
       <c r="I29" s="49" t="n">
         <v>4</v>
@@ -3613,22 +3671,22 @@
         <v>26</v>
       </c>
       <c r="B30" s="48" t="n">
-        <v>64.18000000000001</v>
+        <v>64.25</v>
       </c>
       <c r="C30" s="48" t="n">
-        <v>64.18000000000001</v>
+        <v>192.75</v>
       </c>
       <c r="D30" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="47" t="n">
         <v>26</v>
       </c>
       <c r="G30" s="48" t="n">
-        <v>110.77</v>
+        <v>110.89</v>
       </c>
       <c r="H30" s="48" t="n">
-        <v>443.07</v>
+        <v>443.55</v>
       </c>
       <c r="I30" s="49" t="n">
         <v>4</v>
@@ -3639,22 +3697,22 @@
         <v>27</v>
       </c>
       <c r="B31" s="48" t="n">
-        <v>63.5</v>
+        <v>63.57</v>
       </c>
       <c r="C31" s="48" t="n">
-        <v>63.5</v>
+        <v>190.7</v>
       </c>
       <c r="D31" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" s="47" t="n">
         <v>27</v>
       </c>
       <c r="G31" s="48" t="n">
-        <v>112.02</v>
+        <v>112.14</v>
       </c>
       <c r="H31" s="48" t="n">
-        <v>448.06</v>
+        <v>448.56</v>
       </c>
       <c r="I31" s="49" t="n">
         <v>4</v>
@@ -3665,22 +3723,22 @@
         <v>28</v>
       </c>
       <c r="B32" s="48" t="n">
-        <v>62.81</v>
+        <v>62.88</v>
       </c>
       <c r="C32" s="48" t="n">
-        <v>62.81</v>
+        <v>188.65</v>
       </c>
       <c r="D32" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="47" t="n">
         <v>28</v>
       </c>
       <c r="G32" s="48" t="n">
-        <v>113.28</v>
+        <v>113.4</v>
       </c>
       <c r="H32" s="48" t="n">
-        <v>453.12</v>
+        <v>453.61</v>
       </c>
       <c r="I32" s="49" t="n">
         <v>4</v>
@@ -3691,22 +3749,22 @@
         <v>29</v>
       </c>
       <c r="B33" s="48" t="n">
-        <v>62.13</v>
+        <v>62.2</v>
       </c>
       <c r="C33" s="48" t="n">
-        <v>62.13</v>
+        <v>186.6</v>
       </c>
       <c r="D33" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" s="47" t="n">
         <v>29</v>
       </c>
       <c r="G33" s="48" t="n">
-        <v>114.56</v>
+        <v>114.68</v>
       </c>
       <c r="H33" s="48" t="n">
-        <v>458.23</v>
+        <v>458.73</v>
       </c>
       <c r="I33" s="49" t="n">
         <v>4</v>
@@ -3717,22 +3775,22 @@
         <v>30</v>
       </c>
       <c r="B34" s="48" t="n">
-        <v>61.45</v>
+        <v>61.52</v>
       </c>
       <c r="C34" s="48" t="n">
-        <v>61.45</v>
+        <v>184.55</v>
       </c>
       <c r="D34" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="47" t="n">
         <v>30</v>
       </c>
       <c r="G34" s="48" t="n">
-        <v>115.85</v>
+        <v>115.98</v>
       </c>
       <c r="H34" s="48" t="n">
-        <v>463.4</v>
+        <v>463.91</v>
       </c>
       <c r="I34" s="49" t="n">
         <v>4</v>

--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -1192,10 +1192,10 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="7"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="11"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -1258,22 +1258,22 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="32" t="n">
-        <v>22398.28</v>
+        <v>22268.95</v>
       </c>
       <c r="C4" s="32" t="n">
-        <v>11180.25</v>
+        <v>11050.92</v>
       </c>
       <c r="D4" s="32" t="n">
         <v>11218.03</v>
       </c>
       <c r="E4" s="32" t="n">
-        <v>17216.79</v>
+        <v>18338.593</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>15587.80405</v>
+        <v>16541.3366</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>21089.38195</v>
+        <v>22379.4554</v>
       </c>
       <c r="H4" s="32" t="inlineStr">
         <is>
@@ -1877,19 +1877,19 @@
         <v>136</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>11180.25</v>
+        <v>11050.92</v>
       </c>
       <c r="F15" s="37" t="n">
         <v>11218.03</v>
       </c>
       <c r="G15" s="37" t="n">
-        <v>22398.28</v>
+        <v>22268.95</v>
       </c>
       <c r="H15" s="37" t="n">
-        <v>17216.79</v>
+        <v>18338.59</v>
       </c>
       <c r="I15" s="39" t="n">
-        <v>0.6516</v>
+        <v>0.6117</v>
       </c>
       <c r="J15" s="36" t="inlineStr">
         <is>
@@ -1897,36 +1897,36 @@
         </is>
       </c>
       <c r="K15" s="39" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0612</v>
       </c>
       <c r="L15" s="37" t="n">
+        <v>19460.4</v>
+      </c>
+      <c r="M15" s="37" t="n">
+        <v>16541.34</v>
+      </c>
+      <c r="N15" s="37" t="n">
+        <v>22379.46</v>
+      </c>
+      <c r="O15" s="50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P15" s="37" t="n">
+        <v>8409.48</v>
+      </c>
+      <c r="Q15" s="51" t="n">
+        <v>11050.92</v>
+      </c>
+      <c r="R15" s="51" t="n">
+        <v>16541.34</v>
+      </c>
+      <c r="S15" s="51" t="n">
         <v>18338.59</v>
       </c>
-      <c r="M15" s="37" t="n">
-        <v>15587.8</v>
-      </c>
-      <c r="N15" s="37" t="n">
-        <v>21089.38</v>
-      </c>
-      <c r="O15" s="50" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="P15" s="37" t="n">
-        <v>7158.34</v>
-      </c>
-      <c r="Q15" s="51" t="n">
-        <v>11180.25</v>
-      </c>
-      <c r="R15" s="51" t="n">
-        <v>15587.8</v>
-      </c>
-      <c r="S15" s="51" t="n">
-        <v>17216.79</v>
-      </c>
       <c r="T15" s="51" t="n">
-        <v>21089.38</v>
+        <v>22379.46</v>
       </c>
     </row>
     <row r="16">
@@ -3021,10 +3021,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="48" t="n">
-        <v>81.34</v>
+        <v>80.39</v>
       </c>
       <c r="C5" s="48" t="n">
-        <v>244.01</v>
+        <v>241.18</v>
       </c>
       <c r="D5" s="49" t="n">
         <v>3</v>
@@ -3033,10 +3033,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="48" t="n">
-        <v>83.77</v>
+        <v>82.8</v>
       </c>
       <c r="H5" s="48" t="n">
-        <v>335.1</v>
+        <v>331.22</v>
       </c>
       <c r="I5" s="49" t="n">
         <v>4</v>
@@ -3047,10 +3047,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="48" t="n">
-        <v>80.65000000000001</v>
+        <v>79.72</v>
       </c>
       <c r="C6" s="48" t="n">
-        <v>241.96</v>
+        <v>239.16</v>
       </c>
       <c r="D6" s="49" t="n">
         <v>3</v>
@@ -3059,10 +3059,10 @@
         <v>2</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>84.72</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="H6" s="48" t="n">
-        <v>338.88</v>
+        <v>334.95</v>
       </c>
       <c r="I6" s="49" t="n">
         <v>4</v>
@@ -3073,10 +3073,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="48" t="n">
-        <v>79.97</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="C7" s="48" t="n">
-        <v>239.91</v>
+        <v>237.13</v>
       </c>
       <c r="D7" s="49" t="n">
         <v>3</v>
@@ -3085,10 +3085,10 @@
         <v>3</v>
       </c>
       <c r="G7" s="48" t="n">
-        <v>85.67</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="H7" s="48" t="n">
-        <v>342.7</v>
+        <v>338.73</v>
       </c>
       <c r="I7" s="49" t="n">
         <v>4</v>
@@ -3099,10 +3099,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="48" t="n">
-        <v>79.29000000000001</v>
+        <v>78.37</v>
       </c>
       <c r="C8" s="48" t="n">
-        <v>237.86</v>
+        <v>235.1</v>
       </c>
       <c r="D8" s="49" t="n">
         <v>3</v>
@@ -3111,10 +3111,10 @@
         <v>4</v>
       </c>
       <c r="G8" s="48" t="n">
-        <v>86.64</v>
+        <v>85.64</v>
       </c>
       <c r="H8" s="48" t="n">
-        <v>346.57</v>
+        <v>342.55</v>
       </c>
       <c r="I8" s="49" t="n">
         <v>4</v>
@@ -3125,10 +3125,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="48" t="n">
-        <v>78.59999999999999</v>
+        <v>77.69</v>
       </c>
       <c r="C9" s="48" t="n">
-        <v>235.81</v>
+        <v>233.08</v>
       </c>
       <c r="D9" s="49" t="n">
         <v>3</v>
@@ -3137,10 +3137,10 @@
         <v>5</v>
       </c>
       <c r="G9" s="48" t="n">
-        <v>87.62</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H9" s="48" t="n">
-        <v>350.47</v>
+        <v>346.41</v>
       </c>
       <c r="I9" s="49" t="n">
         <v>4</v>
@@ -3151,10 +3151,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="48" t="n">
-        <v>77.92</v>
+        <v>77.02</v>
       </c>
       <c r="C10" s="48" t="n">
-        <v>233.76</v>
+        <v>231.05</v>
       </c>
       <c r="D10" s="49" t="n">
         <v>3</v>
@@ -3163,10 +3163,10 @@
         <v>6</v>
       </c>
       <c r="G10" s="48" t="n">
-        <v>88.61</v>
+        <v>87.58</v>
       </c>
       <c r="H10" s="48" t="n">
-        <v>354.43</v>
+        <v>350.32</v>
       </c>
       <c r="I10" s="49" t="n">
         <v>4</v>
@@ -3177,10 +3177,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="48" t="n">
-        <v>77.23999999999999</v>
+        <v>76.34</v>
       </c>
       <c r="C11" s="48" t="n">
-        <v>231.71</v>
+        <v>229.02</v>
       </c>
       <c r="D11" s="49" t="n">
         <v>3</v>
@@ -3189,10 +3189,10 @@
         <v>7</v>
       </c>
       <c r="G11" s="48" t="n">
-        <v>89.61</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H11" s="48" t="n">
-        <v>358.42</v>
+        <v>354.27</v>
       </c>
       <c r="I11" s="49" t="n">
         <v>4</v>
@@ -3203,10 +3203,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="48" t="n">
-        <v>76.55</v>
+        <v>75.67</v>
       </c>
       <c r="C12" s="48" t="n">
-        <v>229.66</v>
+        <v>227</v>
       </c>
       <c r="D12" s="49" t="n">
         <v>3</v>
@@ -3215,10 +3215,10 @@
         <v>8</v>
       </c>
       <c r="G12" s="48" t="n">
-        <v>90.62</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="H12" s="48" t="n">
-        <v>362.47</v>
+        <v>358.27</v>
       </c>
       <c r="I12" s="49" t="n">
         <v>4</v>
@@ -3229,10 +3229,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="48" t="n">
-        <v>75.87</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="C13" s="48" t="n">
-        <v>227.61</v>
+        <v>224.97</v>
       </c>
       <c r="D13" s="49" t="n">
         <v>3</v>
@@ -3241,10 +3241,10 @@
         <v>9</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>91.64</v>
+        <v>90.58</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>366.56</v>
+        <v>362.31</v>
       </c>
       <c r="I13" s="49" t="n">
         <v>4</v>
@@ -3255,10 +3255,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="48" t="n">
-        <v>75.19</v>
+        <v>74.31</v>
       </c>
       <c r="C14" s="48" t="n">
-        <v>225.56</v>
+        <v>222.94</v>
       </c>
       <c r="D14" s="49" t="n">
         <v>3</v>
@@ -3267,10 +3267,10 @@
         <v>10</v>
       </c>
       <c r="G14" s="48" t="n">
-        <v>92.67</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H14" s="48" t="n">
-        <v>370.69</v>
+        <v>366.4</v>
       </c>
       <c r="I14" s="49" t="n">
         <v>4</v>
@@ -3281,10 +3281,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="48" t="n">
-        <v>74.5</v>
+        <v>73.64</v>
       </c>
       <c r="C15" s="48" t="n">
-        <v>223.5</v>
+        <v>220.92</v>
       </c>
       <c r="D15" s="49" t="n">
         <v>3</v>
@@ -3293,10 +3293,10 @@
         <v>11</v>
       </c>
       <c r="G15" s="48" t="n">
-        <v>93.72</v>
+        <v>92.63</v>
       </c>
       <c r="H15" s="48" t="n">
-        <v>374.87</v>
+        <v>370.53</v>
       </c>
       <c r="I15" s="49" t="n">
         <v>4</v>
@@ -3307,10 +3307,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="48" t="n">
-        <v>73.81999999999999</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="C16" s="48" t="n">
-        <v>221.45</v>
+        <v>218.89</v>
       </c>
       <c r="D16" s="49" t="n">
         <v>3</v>
@@ -3319,10 +3319,10 @@
         <v>12</v>
       </c>
       <c r="G16" s="48" t="n">
-        <v>94.77</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="H16" s="48" t="n">
-        <v>379.1</v>
+        <v>374.71</v>
       </c>
       <c r="I16" s="49" t="n">
         <v>4</v>
@@ -3333,10 +3333,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="48" t="n">
-        <v>73.13</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="C17" s="48" t="n">
-        <v>219.4</v>
+        <v>216.86</v>
       </c>
       <c r="D17" s="49" t="n">
         <v>3</v>
@@ -3345,10 +3345,10 @@
         <v>13</v>
       </c>
       <c r="G17" s="48" t="n">
-        <v>95.84</v>
+        <v>94.73</v>
       </c>
       <c r="H17" s="48" t="n">
-        <v>383.37</v>
+        <v>378.93</v>
       </c>
       <c r="I17" s="49" t="n">
         <v>4</v>
@@ -3359,10 +3359,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="48" t="n">
-        <v>72.45</v>
+        <v>71.61</v>
       </c>
       <c r="C18" s="48" t="n">
-        <v>217.35</v>
+        <v>214.84</v>
       </c>
       <c r="D18" s="49" t="n">
         <v>3</v>
@@ -3371,10 +3371,10 @@
         <v>14</v>
       </c>
       <c r="G18" s="48" t="n">
-        <v>96.92</v>
+        <v>95.8</v>
       </c>
       <c r="H18" s="48" t="n">
-        <v>387.7</v>
+        <v>383.21</v>
       </c>
       <c r="I18" s="49" t="n">
         <v>4</v>
@@ -3385,10 +3385,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="48" t="n">
-        <v>71.77</v>
+        <v>70.94</v>
       </c>
       <c r="C19" s="48" t="n">
-        <v>215.3</v>
+        <v>212.81</v>
       </c>
       <c r="D19" s="49" t="n">
         <v>3</v>
@@ -3397,10 +3397,10 @@
         <v>15</v>
       </c>
       <c r="G19" s="48" t="n">
-        <v>98.02</v>
+        <v>96.88</v>
       </c>
       <c r="H19" s="48" t="n">
-        <v>392.07</v>
+        <v>387.53</v>
       </c>
       <c r="I19" s="49" t="n">
         <v>4</v>
@@ -3411,10 +3411,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="48" t="n">
-        <v>71.08</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="C20" s="48" t="n">
-        <v>213.25</v>
+        <v>210.78</v>
       </c>
       <c r="D20" s="49" t="n">
         <v>3</v>
@@ -3423,10 +3423,10 @@
         <v>16</v>
       </c>
       <c r="G20" s="48" t="n">
-        <v>99.12</v>
+        <v>97.98</v>
       </c>
       <c r="H20" s="48" t="n">
-        <v>396.49</v>
+        <v>391.9</v>
       </c>
       <c r="I20" s="49" t="n">
         <v>4</v>
@@ -3437,10 +3437,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="48" t="n">
-        <v>70.40000000000001</v>
+        <v>69.59</v>
       </c>
       <c r="C21" s="48" t="n">
-        <v>211.2</v>
+        <v>208.76</v>
       </c>
       <c r="D21" s="49" t="n">
         <v>3</v>
@@ -3449,10 +3449,10 @@
         <v>17</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>100.24</v>
+        <v>99.08</v>
       </c>
       <c r="H21" s="48" t="n">
-        <v>400.97</v>
+        <v>396.32</v>
       </c>
       <c r="I21" s="49" t="n">
         <v>4</v>
@@ -3463,10 +3463,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="48" t="n">
-        <v>69.72</v>
+        <v>68.91</v>
       </c>
       <c r="C22" s="48" t="n">
-        <v>209.15</v>
+        <v>206.73</v>
       </c>
       <c r="D22" s="49" t="n">
         <v>3</v>
@@ -3475,10 +3475,10 @@
         <v>18</v>
       </c>
       <c r="G22" s="48" t="n">
-        <v>101.37</v>
+        <v>100.2</v>
       </c>
       <c r="H22" s="48" t="n">
-        <v>405.49</v>
+        <v>400.79</v>
       </c>
       <c r="I22" s="49" t="n">
         <v>4</v>
@@ -3489,10 +3489,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="48" t="n">
-        <v>69.03</v>
+        <v>68.23</v>
       </c>
       <c r="C23" s="48" t="n">
-        <v>207.1</v>
+        <v>204.7</v>
       </c>
       <c r="D23" s="49" t="n">
         <v>3</v>
@@ -3501,10 +3501,10 @@
         <v>19</v>
       </c>
       <c r="G23" s="48" t="n">
-        <v>102.52</v>
+        <v>101.33</v>
       </c>
       <c r="H23" s="48" t="n">
-        <v>410.06</v>
+        <v>405.31</v>
       </c>
       <c r="I23" s="49" t="n">
         <v>4</v>
@@ -3515,10 +3515,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="48" t="n">
-        <v>68.34999999999999</v>
+        <v>67.56</v>
       </c>
       <c r="C24" s="48" t="n">
-        <v>205.05</v>
+        <v>202.67</v>
       </c>
       <c r="D24" s="49" t="n">
         <v>3</v>
@@ -3527,10 +3527,10 @@
         <v>20</v>
       </c>
       <c r="G24" s="48" t="n">
-        <v>103.67</v>
+        <v>102.47</v>
       </c>
       <c r="H24" s="48" t="n">
-        <v>414.69</v>
+        <v>409.88</v>
       </c>
       <c r="I24" s="49" t="n">
         <v>4</v>
@@ -3541,10 +3541,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="48" t="n">
-        <v>67.67</v>
+        <v>66.88</v>
       </c>
       <c r="C25" s="48" t="n">
-        <v>203</v>
+        <v>200.65</v>
       </c>
       <c r="D25" s="49" t="n">
         <v>3</v>
@@ -3553,10 +3553,10 @@
         <v>21</v>
       </c>
       <c r="G25" s="48" t="n">
-        <v>104.84</v>
+        <v>103.63</v>
       </c>
       <c r="H25" s="48" t="n">
-        <v>419.36</v>
+        <v>414.51</v>
       </c>
       <c r="I25" s="49" t="n">
         <v>4</v>
@@ -3567,10 +3567,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="48" t="n">
-        <v>66.98</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="C26" s="48" t="n">
-        <v>200.95</v>
+        <v>198.62</v>
       </c>
       <c r="D26" s="49" t="n">
         <v>3</v>
@@ -3579,10 +3579,10 @@
         <v>22</v>
       </c>
       <c r="G26" s="48" t="n">
-        <v>106.02</v>
+        <v>104.8</v>
       </c>
       <c r="H26" s="48" t="n">
-        <v>424.09</v>
+        <v>419.18</v>
       </c>
       <c r="I26" s="49" t="n">
         <v>4</v>
@@ -3593,10 +3593,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="48" t="n">
-        <v>66.3</v>
+        <v>65.53</v>
       </c>
       <c r="C27" s="48" t="n">
-        <v>198.9</v>
+        <v>196.59</v>
       </c>
       <c r="D27" s="49" t="n">
         <v>3</v>
@@ -3605,10 +3605,10 @@
         <v>23</v>
       </c>
       <c r="G27" s="48" t="n">
-        <v>107.22</v>
+        <v>105.98</v>
       </c>
       <c r="H27" s="48" t="n">
-        <v>428.88</v>
+        <v>423.91</v>
       </c>
       <c r="I27" s="49" t="n">
         <v>4</v>
@@ -3619,10 +3619,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="48" t="n">
-        <v>65.62</v>
+        <v>64.86</v>
       </c>
       <c r="C28" s="48" t="n">
-        <v>196.85</v>
+        <v>194.57</v>
       </c>
       <c r="D28" s="49" t="n">
         <v>3</v>
@@ -3631,10 +3631,10 @@
         <v>24</v>
       </c>
       <c r="G28" s="48" t="n">
-        <v>108.43</v>
+        <v>107.17</v>
       </c>
       <c r="H28" s="48" t="n">
-        <v>433.71</v>
+        <v>428.69</v>
       </c>
       <c r="I28" s="49" t="n">
         <v>4</v>
@@ -3645,10 +3645,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="48" t="n">
-        <v>64.93000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="C29" s="48" t="n">
-        <v>194.8</v>
+        <v>192.54</v>
       </c>
       <c r="D29" s="49" t="n">
         <v>3</v>
@@ -3657,10 +3657,10 @@
         <v>25</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>109.65</v>
+        <v>108.38</v>
       </c>
       <c r="H29" s="48" t="n">
-        <v>438.61</v>
+        <v>433.53</v>
       </c>
       <c r="I29" s="49" t="n">
         <v>4</v>
@@ -3671,10 +3671,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="48" t="n">
-        <v>64.25</v>
+        <v>63.5</v>
       </c>
       <c r="C30" s="48" t="n">
-        <v>192.75</v>
+        <v>190.51</v>
       </c>
       <c r="D30" s="49" t="n">
         <v>3</v>
@@ -3683,10 +3683,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="48" t="n">
-        <v>110.89</v>
+        <v>109.6</v>
       </c>
       <c r="H30" s="48" t="n">
-        <v>443.55</v>
+        <v>438.42</v>
       </c>
       <c r="I30" s="49" t="n">
         <v>4</v>
@@ -3697,10 +3697,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="48" t="n">
-        <v>63.57</v>
+        <v>62.83</v>
       </c>
       <c r="C31" s="48" t="n">
-        <v>190.7</v>
+        <v>188.49</v>
       </c>
       <c r="D31" s="49" t="n">
         <v>3</v>
@@ -3709,10 +3709,10 @@
         <v>27</v>
       </c>
       <c r="G31" s="48" t="n">
-        <v>112.14</v>
+        <v>110.84</v>
       </c>
       <c r="H31" s="48" t="n">
-        <v>448.56</v>
+        <v>443.36</v>
       </c>
       <c r="I31" s="49" t="n">
         <v>4</v>
@@ -3723,10 +3723,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="48" t="n">
-        <v>62.88</v>
+        <v>62.15</v>
       </c>
       <c r="C32" s="48" t="n">
-        <v>188.65</v>
+        <v>186.46</v>
       </c>
       <c r="D32" s="49" t="n">
         <v>3</v>
@@ -3735,10 +3735,10 @@
         <v>28</v>
       </c>
       <c r="G32" s="48" t="n">
-        <v>113.4</v>
+        <v>112.09</v>
       </c>
       <c r="H32" s="48" t="n">
-        <v>453.61</v>
+        <v>448.36</v>
       </c>
       <c r="I32" s="49" t="n">
         <v>4</v>
@@ -3749,10 +3749,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="48" t="n">
-        <v>62.2</v>
+        <v>61.48</v>
       </c>
       <c r="C33" s="48" t="n">
-        <v>186.6</v>
+        <v>184.43</v>
       </c>
       <c r="D33" s="49" t="n">
         <v>3</v>
@@ -3761,10 +3761,10 @@
         <v>29</v>
       </c>
       <c r="G33" s="48" t="n">
-        <v>114.68</v>
+        <v>113.35</v>
       </c>
       <c r="H33" s="48" t="n">
-        <v>458.73</v>
+        <v>453.42</v>
       </c>
       <c r="I33" s="49" t="n">
         <v>4</v>
@@ -3775,10 +3775,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="48" t="n">
-        <v>61.52</v>
+        <v>60.8</v>
       </c>
       <c r="C34" s="48" t="n">
-        <v>184.55</v>
+        <v>182.41</v>
       </c>
       <c r="D34" s="49" t="n">
         <v>3</v>
@@ -3787,10 +3787,10 @@
         <v>30</v>
       </c>
       <c r="G34" s="48" t="n">
-        <v>115.98</v>
+        <v>114.63</v>
       </c>
       <c r="H34" s="48" t="n">
-        <v>463.91</v>
+        <v>458.53</v>
       </c>
       <c r="I34" s="49" t="n">
         <v>4</v>

--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -1192,7 +1192,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="7"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="32" t="n">
-        <v>22268.95</v>
+        <v>22266.26</v>
       </c>
       <c r="C4" s="32" t="n">
-        <v>11050.92</v>
+        <v>11048.23</v>
       </c>
       <c r="D4" s="32" t="n">
         <v>11218.03</v>
@@ -1877,13 +1877,13 @@
         <v>136</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>11050.92</v>
+        <v>11048.23</v>
       </c>
       <c r="F15" s="37" t="n">
         <v>11218.03</v>
       </c>
       <c r="G15" s="37" t="n">
-        <v>22268.95</v>
+        <v>22266.26</v>
       </c>
       <c r="H15" s="37" t="n">
         <v>18338.59</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="P15" s="37" t="n">
-        <v>8409.48</v>
+        <v>8412.17</v>
       </c>
       <c r="Q15" s="51" t="n">
-        <v>11050.92</v>
+        <v>11048.23</v>
       </c>
       <c r="R15" s="51" t="n">
         <v>16541.34</v>
@@ -3021,10 +3021,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="48" t="n">
-        <v>80.39</v>
+        <v>80.37</v>
       </c>
       <c r="C5" s="48" t="n">
-        <v>241.18</v>
+        <v>241.12</v>
       </c>
       <c r="D5" s="49" t="n">
         <v>3</v>
@@ -3033,10 +3033,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="48" t="n">
-        <v>82.8</v>
+        <v>82.78</v>
       </c>
       <c r="H5" s="48" t="n">
-        <v>331.22</v>
+        <v>331.14</v>
       </c>
       <c r="I5" s="49" t="n">
         <v>4</v>
@@ -3047,10 +3047,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="48" t="n">
-        <v>79.72</v>
+        <v>79.7</v>
       </c>
       <c r="C6" s="48" t="n">
-        <v>239.16</v>
+        <v>239.1</v>
       </c>
       <c r="D6" s="49" t="n">
         <v>3</v>
@@ -3059,10 +3059,10 @@
         <v>2</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>83.73999999999999</v>
+        <v>83.72</v>
       </c>
       <c r="H6" s="48" t="n">
-        <v>334.95</v>
+        <v>334.87</v>
       </c>
       <c r="I6" s="49" t="n">
         <v>4</v>
@@ -3073,10 +3073,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="48" t="n">
-        <v>79.04000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="C7" s="48" t="n">
-        <v>237.13</v>
+        <v>237.07</v>
       </c>
       <c r="D7" s="49" t="n">
         <v>3</v>
@@ -3085,10 +3085,10 @@
         <v>3</v>
       </c>
       <c r="G7" s="48" t="n">
-        <v>84.68000000000001</v>
+        <v>84.66</v>
       </c>
       <c r="H7" s="48" t="n">
-        <v>338.73</v>
+        <v>338.65</v>
       </c>
       <c r="I7" s="49" t="n">
         <v>4</v>
@@ -3099,10 +3099,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="48" t="n">
-        <v>78.37</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="C8" s="48" t="n">
-        <v>235.1</v>
+        <v>235.04</v>
       </c>
       <c r="D8" s="49" t="n">
         <v>3</v>
@@ -3111,10 +3111,10 @@
         <v>4</v>
       </c>
       <c r="G8" s="48" t="n">
-        <v>85.64</v>
+        <v>85.62</v>
       </c>
       <c r="H8" s="48" t="n">
-        <v>342.55</v>
+        <v>342.47</v>
       </c>
       <c r="I8" s="49" t="n">
         <v>4</v>
@@ -3125,10 +3125,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="48" t="n">
-        <v>77.69</v>
+        <v>77.67</v>
       </c>
       <c r="C9" s="48" t="n">
-        <v>233.08</v>
+        <v>233.02</v>
       </c>
       <c r="D9" s="49" t="n">
         <v>3</v>
@@ -3137,10 +3137,10 @@
         <v>5</v>
       </c>
       <c r="G9" s="48" t="n">
-        <v>86.59999999999999</v>
+        <v>86.58</v>
       </c>
       <c r="H9" s="48" t="n">
-        <v>346.41</v>
+        <v>346.33</v>
       </c>
       <c r="I9" s="49" t="n">
         <v>4</v>
@@ -3151,10 +3151,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="48" t="n">
-        <v>77.02</v>
+        <v>77</v>
       </c>
       <c r="C10" s="48" t="n">
-        <v>231.05</v>
+        <v>230.99</v>
       </c>
       <c r="D10" s="49" t="n">
         <v>3</v>
@@ -3163,10 +3163,10 @@
         <v>6</v>
       </c>
       <c r="G10" s="48" t="n">
-        <v>87.58</v>
+        <v>87.56</v>
       </c>
       <c r="H10" s="48" t="n">
-        <v>350.32</v>
+        <v>350.24</v>
       </c>
       <c r="I10" s="49" t="n">
         <v>4</v>
@@ -3177,10 +3177,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="48" t="n">
-        <v>76.34</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="C11" s="48" t="n">
-        <v>229.02</v>
+        <v>228.97</v>
       </c>
       <c r="D11" s="49" t="n">
         <v>3</v>
@@ -3189,10 +3189,10 @@
         <v>7</v>
       </c>
       <c r="G11" s="48" t="n">
-        <v>88.56999999999999</v>
+        <v>88.55</v>
       </c>
       <c r="H11" s="48" t="n">
-        <v>354.27</v>
+        <v>354.19</v>
       </c>
       <c r="I11" s="49" t="n">
         <v>4</v>
@@ -3203,10 +3203,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="48" t="n">
-        <v>75.67</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="C12" s="48" t="n">
-        <v>227</v>
+        <v>226.94</v>
       </c>
       <c r="D12" s="49" t="n">
         <v>3</v>
@@ -3215,10 +3215,10 @@
         <v>8</v>
       </c>
       <c r="G12" s="48" t="n">
-        <v>89.56999999999999</v>
+        <v>89.55</v>
       </c>
       <c r="H12" s="48" t="n">
-        <v>358.27</v>
+        <v>358.18</v>
       </c>
       <c r="I12" s="49" t="n">
         <v>4</v>
@@ -3229,10 +3229,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="48" t="n">
-        <v>74.98999999999999</v>
+        <v>74.97</v>
       </c>
       <c r="C13" s="48" t="n">
-        <v>224.97</v>
+        <v>224.91</v>
       </c>
       <c r="D13" s="49" t="n">
         <v>3</v>
@@ -3241,10 +3241,10 @@
         <v>9</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>90.58</v>
+        <v>90.56</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>362.31</v>
+        <v>362.22</v>
       </c>
       <c r="I13" s="49" t="n">
         <v>4</v>
@@ -3255,10 +3255,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="48" t="n">
-        <v>74.31</v>
+        <v>74.3</v>
       </c>
       <c r="C14" s="48" t="n">
-        <v>222.94</v>
+        <v>222.89</v>
       </c>
       <c r="D14" s="49" t="n">
         <v>3</v>
@@ -3267,10 +3267,10 @@
         <v>10</v>
       </c>
       <c r="G14" s="48" t="n">
-        <v>91.59999999999999</v>
+        <v>91.58</v>
       </c>
       <c r="H14" s="48" t="n">
-        <v>366.4</v>
+        <v>366.31</v>
       </c>
       <c r="I14" s="49" t="n">
         <v>4</v>
@@ -3281,10 +3281,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="48" t="n">
-        <v>73.64</v>
+        <v>73.62</v>
       </c>
       <c r="C15" s="48" t="n">
-        <v>220.92</v>
+        <v>220.86</v>
       </c>
       <c r="D15" s="49" t="n">
         <v>3</v>
@@ -3293,10 +3293,10 @@
         <v>11</v>
       </c>
       <c r="G15" s="48" t="n">
-        <v>92.63</v>
+        <v>92.61</v>
       </c>
       <c r="H15" s="48" t="n">
-        <v>370.53</v>
+        <v>370.44</v>
       </c>
       <c r="I15" s="49" t="n">
         <v>4</v>
@@ -3307,10 +3307,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="48" t="n">
-        <v>72.95999999999999</v>
+        <v>72.94</v>
       </c>
       <c r="C16" s="48" t="n">
-        <v>218.89</v>
+        <v>218.83</v>
       </c>
       <c r="D16" s="49" t="n">
         <v>3</v>
@@ -3319,10 +3319,10 @@
         <v>12</v>
       </c>
       <c r="G16" s="48" t="n">
-        <v>93.68000000000001</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="H16" s="48" t="n">
-        <v>374.71</v>
+        <v>374.62</v>
       </c>
       <c r="I16" s="49" t="n">
         <v>4</v>
@@ -3333,10 +3333,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="48" t="n">
-        <v>72.29000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="C17" s="48" t="n">
-        <v>216.86</v>
+        <v>216.81</v>
       </c>
       <c r="D17" s="49" t="n">
         <v>3</v>
@@ -3345,10 +3345,10 @@
         <v>13</v>
       </c>
       <c r="G17" s="48" t="n">
-        <v>94.73</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="H17" s="48" t="n">
-        <v>378.93</v>
+        <v>378.84</v>
       </c>
       <c r="I17" s="49" t="n">
         <v>4</v>
@@ -3359,10 +3359,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="48" t="n">
-        <v>71.61</v>
+        <v>71.59</v>
       </c>
       <c r="C18" s="48" t="n">
-        <v>214.84</v>
+        <v>214.78</v>
       </c>
       <c r="D18" s="49" t="n">
         <v>3</v>
@@ -3371,10 +3371,10 @@
         <v>14</v>
       </c>
       <c r="G18" s="48" t="n">
-        <v>95.8</v>
+        <v>95.78</v>
       </c>
       <c r="H18" s="48" t="n">
-        <v>383.21</v>
+        <v>383.11</v>
       </c>
       <c r="I18" s="49" t="n">
         <v>4</v>
@@ -3385,10 +3385,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="48" t="n">
-        <v>70.94</v>
+        <v>70.92</v>
       </c>
       <c r="C19" s="48" t="n">
-        <v>212.81</v>
+        <v>212.76</v>
       </c>
       <c r="D19" s="49" t="n">
         <v>3</v>
@@ -3397,10 +3397,10 @@
         <v>15</v>
       </c>
       <c r="G19" s="48" t="n">
-        <v>96.88</v>
+        <v>96.86</v>
       </c>
       <c r="H19" s="48" t="n">
-        <v>387.53</v>
+        <v>387.43</v>
       </c>
       <c r="I19" s="49" t="n">
         <v>4</v>
@@ -3411,10 +3411,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="48" t="n">
-        <v>70.26000000000001</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="C20" s="48" t="n">
-        <v>210.78</v>
+        <v>210.73</v>
       </c>
       <c r="D20" s="49" t="n">
         <v>3</v>
@@ -3423,10 +3423,10 @@
         <v>16</v>
       </c>
       <c r="G20" s="48" t="n">
-        <v>97.98</v>
+        <v>97.95</v>
       </c>
       <c r="H20" s="48" t="n">
-        <v>391.9</v>
+        <v>391.8</v>
       </c>
       <c r="I20" s="49" t="n">
         <v>4</v>
@@ -3437,10 +3437,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="48" t="n">
-        <v>69.59</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="C21" s="48" t="n">
-        <v>208.76</v>
+        <v>208.7</v>
       </c>
       <c r="D21" s="49" t="n">
         <v>3</v>
@@ -3449,10 +3449,10 @@
         <v>17</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>99.08</v>
+        <v>99.06</v>
       </c>
       <c r="H21" s="48" t="n">
-        <v>396.32</v>
+        <v>396.22</v>
       </c>
       <c r="I21" s="49" t="n">
         <v>4</v>
@@ -3463,10 +3463,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="48" t="n">
-        <v>68.91</v>
+        <v>68.89</v>
       </c>
       <c r="C22" s="48" t="n">
-        <v>206.73</v>
+        <v>206.68</v>
       </c>
       <c r="D22" s="49" t="n">
         <v>3</v>
@@ -3475,10 +3475,10 @@
         <v>18</v>
       </c>
       <c r="G22" s="48" t="n">
-        <v>100.2</v>
+        <v>100.17</v>
       </c>
       <c r="H22" s="48" t="n">
-        <v>400.79</v>
+        <v>400.69</v>
       </c>
       <c r="I22" s="49" t="n">
         <v>4</v>
@@ -3489,10 +3489,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="48" t="n">
-        <v>68.23</v>
+        <v>68.22</v>
       </c>
       <c r="C23" s="48" t="n">
-        <v>204.7</v>
+        <v>204.65</v>
       </c>
       <c r="D23" s="49" t="n">
         <v>3</v>
@@ -3501,10 +3501,10 @@
         <v>19</v>
       </c>
       <c r="G23" s="48" t="n">
-        <v>101.33</v>
+        <v>101.3</v>
       </c>
       <c r="H23" s="48" t="n">
-        <v>405.31</v>
+        <v>405.21</v>
       </c>
       <c r="I23" s="49" t="n">
         <v>4</v>
@@ -3515,10 +3515,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="48" t="n">
-        <v>67.56</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="C24" s="48" t="n">
-        <v>202.67</v>
+        <v>202.62</v>
       </c>
       <c r="D24" s="49" t="n">
         <v>3</v>
@@ -3527,10 +3527,10 @@
         <v>20</v>
       </c>
       <c r="G24" s="48" t="n">
-        <v>102.47</v>
+        <v>102.45</v>
       </c>
       <c r="H24" s="48" t="n">
-        <v>409.88</v>
+        <v>409.78</v>
       </c>
       <c r="I24" s="49" t="n">
         <v>4</v>
@@ -3541,10 +3541,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="48" t="n">
-        <v>66.88</v>
+        <v>66.87</v>
       </c>
       <c r="C25" s="48" t="n">
-        <v>200.65</v>
+        <v>200.6</v>
       </c>
       <c r="D25" s="49" t="n">
         <v>3</v>
@@ -3553,10 +3553,10 @@
         <v>21</v>
       </c>
       <c r="G25" s="48" t="n">
-        <v>103.63</v>
+        <v>103.6</v>
       </c>
       <c r="H25" s="48" t="n">
-        <v>414.51</v>
+        <v>414.4</v>
       </c>
       <c r="I25" s="49" t="n">
         <v>4</v>
@@ -3567,10 +3567,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="48" t="n">
-        <v>66.20999999999999</v>
+        <v>66.19</v>
       </c>
       <c r="C26" s="48" t="n">
-        <v>198.62</v>
+        <v>198.57</v>
       </c>
       <c r="D26" s="49" t="n">
         <v>3</v>
@@ -3579,10 +3579,10 @@
         <v>22</v>
       </c>
       <c r="G26" s="48" t="n">
-        <v>104.8</v>
+        <v>104.77</v>
       </c>
       <c r="H26" s="48" t="n">
-        <v>419.18</v>
+        <v>419.08</v>
       </c>
       <c r="I26" s="49" t="n">
         <v>4</v>
@@ -3593,10 +3593,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="48" t="n">
-        <v>65.53</v>
+        <v>65.52</v>
       </c>
       <c r="C27" s="48" t="n">
-        <v>196.59</v>
+        <v>196.55</v>
       </c>
       <c r="D27" s="49" t="n">
         <v>3</v>
@@ -3605,10 +3605,10 @@
         <v>23</v>
       </c>
       <c r="G27" s="48" t="n">
-        <v>105.98</v>
+        <v>105.95</v>
       </c>
       <c r="H27" s="48" t="n">
-        <v>423.91</v>
+        <v>423.8</v>
       </c>
       <c r="I27" s="49" t="n">
         <v>4</v>
@@ -3619,10 +3619,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="48" t="n">
-        <v>64.86</v>
+        <v>64.84</v>
       </c>
       <c r="C28" s="48" t="n">
-        <v>194.57</v>
+        <v>194.52</v>
       </c>
       <c r="D28" s="49" t="n">
         <v>3</v>
@@ -3631,10 +3631,10 @@
         <v>24</v>
       </c>
       <c r="G28" s="48" t="n">
-        <v>107.17</v>
+        <v>107.15</v>
       </c>
       <c r="H28" s="48" t="n">
-        <v>428.69</v>
+        <v>428.58</v>
       </c>
       <c r="I28" s="49" t="n">
         <v>4</v>
@@ -3645,10 +3645,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="48" t="n">
-        <v>64.18000000000001</v>
+        <v>64.16</v>
       </c>
       <c r="C29" s="48" t="n">
-        <v>192.54</v>
+        <v>192.49</v>
       </c>
       <c r="D29" s="49" t="n">
         <v>3</v>
@@ -3657,10 +3657,10 @@
         <v>25</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>108.38</v>
+        <v>108.35</v>
       </c>
       <c r="H29" s="48" t="n">
-        <v>433.53</v>
+        <v>433.42</v>
       </c>
       <c r="I29" s="49" t="n">
         <v>4</v>
@@ -3671,10 +3671,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="48" t="n">
-        <v>63.5</v>
+        <v>63.49</v>
       </c>
       <c r="C30" s="48" t="n">
-        <v>190.51</v>
+        <v>190.47</v>
       </c>
       <c r="D30" s="49" t="n">
         <v>3</v>
@@ -3683,10 +3683,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="48" t="n">
-        <v>109.6</v>
+        <v>109.58</v>
       </c>
       <c r="H30" s="48" t="n">
-        <v>438.42</v>
+        <v>438.31</v>
       </c>
       <c r="I30" s="49" t="n">
         <v>4</v>
@@ -3697,10 +3697,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="48" t="n">
-        <v>62.83</v>
+        <v>62.81</v>
       </c>
       <c r="C31" s="48" t="n">
-        <v>188.49</v>
+        <v>188.44</v>
       </c>
       <c r="D31" s="49" t="n">
         <v>3</v>
@@ -3709,10 +3709,10 @@
         <v>27</v>
       </c>
       <c r="G31" s="48" t="n">
-        <v>110.84</v>
+        <v>110.81</v>
       </c>
       <c r="H31" s="48" t="n">
-        <v>443.36</v>
+        <v>443.25</v>
       </c>
       <c r="I31" s="49" t="n">
         <v>4</v>
@@ -3723,10 +3723,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="48" t="n">
-        <v>62.15</v>
+        <v>62.14</v>
       </c>
       <c r="C32" s="48" t="n">
-        <v>186.46</v>
+        <v>186.41</v>
       </c>
       <c r="D32" s="49" t="n">
         <v>3</v>
@@ -3735,10 +3735,10 @@
         <v>28</v>
       </c>
       <c r="G32" s="48" t="n">
-        <v>112.09</v>
+        <v>112.06</v>
       </c>
       <c r="H32" s="48" t="n">
-        <v>448.36</v>
+        <v>448.25</v>
       </c>
       <c r="I32" s="49" t="n">
         <v>4</v>
@@ -3749,10 +3749,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="48" t="n">
-        <v>61.48</v>
+        <v>61.46</v>
       </c>
       <c r="C33" s="48" t="n">
-        <v>184.43</v>
+        <v>184.39</v>
       </c>
       <c r="D33" s="49" t="n">
         <v>3</v>
@@ -3761,10 +3761,10 @@
         <v>29</v>
       </c>
       <c r="G33" s="48" t="n">
-        <v>113.35</v>
+        <v>113.33</v>
       </c>
       <c r="H33" s="48" t="n">
-        <v>453.42</v>
+        <v>453.31</v>
       </c>
       <c r="I33" s="49" t="n">
         <v>4</v>
@@ -3775,10 +3775,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="48" t="n">
-        <v>60.8</v>
+        <v>60.79</v>
       </c>
       <c r="C34" s="48" t="n">
-        <v>182.41</v>
+        <v>182.36</v>
       </c>
       <c r="D34" s="49" t="n">
         <v>3</v>
@@ -3787,10 +3787,10 @@
         <v>30</v>
       </c>
       <c r="G34" s="48" t="n">
-        <v>114.63</v>
+        <v>114.6</v>
       </c>
       <c r="H34" s="48" t="n">
-        <v>458.53</v>
+        <v>458.42</v>
       </c>
       <c r="I34" s="49" t="n">
         <v>4</v>

--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -1192,7 +1192,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="7"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="32" t="n">
-        <v>22266.26</v>
+        <v>22266.25</v>
       </c>
       <c r="C4" s="32" t="n">
-        <v>11048.23</v>
+        <v>11048.22</v>
       </c>
       <c r="D4" s="32" t="n">
         <v>11218.03</v>
@@ -1877,13 +1877,13 @@
         <v>136</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>11048.23</v>
+        <v>11048.22</v>
       </c>
       <c r="F15" s="37" t="n">
         <v>11218.03</v>
       </c>
       <c r="G15" s="37" t="n">
-        <v>22266.26</v>
+        <v>22266.25</v>
       </c>
       <c r="H15" s="37" t="n">
         <v>18338.59</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="P15" s="37" t="n">
-        <v>8412.17</v>
+        <v>8412.18</v>
       </c>
       <c r="Q15" s="51" t="n">
-        <v>11048.23</v>
+        <v>11048.22</v>
       </c>
       <c r="R15" s="51" t="n">
         <v>16541.34</v>

--- a/vr_portfolio_log.xlsx
+++ b/vr_portfolio_log.xlsx
@@ -471,12 +471,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$15</f>
+              <f>'루나시트 VR일지'!$B$8:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$E$8:$E$15</f>
+              <f>'루나시트 VR일지'!$E$8:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -503,12 +503,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$15</f>
+              <f>'루나시트 VR일지'!$B$8:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$F$8:$F$15</f>
+              <f>'루나시트 VR일지'!$F$8:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -535,12 +535,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$15</f>
+              <f>'루나시트 VR일지'!$B$8:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$G$8:$G$15</f>
+              <f>'루나시트 VR일지'!$G$8:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -666,12 +666,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$15</f>
+              <f>'루나시트 VR일지'!$B$8:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$Q$8:$Q$15</f>
+              <f>'루나시트 VR일지'!$Q$8:$Q$16</f>
             </numRef>
           </val>
         </ser>
@@ -698,12 +698,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$15</f>
+              <f>'루나시트 VR일지'!$B$8:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$R$8:$R$15</f>
+              <f>'루나시트 VR일지'!$R$8:$R$16</f>
             </numRef>
           </val>
         </ser>
@@ -730,12 +730,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$15</f>
+              <f>'루나시트 VR일지'!$B$8:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$S$8:$S$15</f>
+              <f>'루나시트 VR일지'!$S$8:$S$16</f>
             </numRef>
           </val>
         </ser>
@@ -762,12 +762,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'루나시트 VR일지'!$B$8:$B$15</f>
+              <f>'루나시트 VR일지'!$B$8:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'루나시트 VR일지'!$T$8:$T$15</f>
+              <f>'루나시트 VR일지'!$T$8:$T$16</f>
             </numRef>
           </val>
         </ser>
@@ -1191,11 +1191,11 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="7"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="6" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="11"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -1258,26 +1258,26 @@
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="32" t="n">
-        <v>22266.25</v>
+        <v>20631.21</v>
       </c>
       <c r="C4" s="32" t="n">
-        <v>11048.22</v>
+        <v>16689.04</v>
       </c>
       <c r="D4" s="32" t="n">
-        <v>11218.03</v>
+        <v>3942.169999999998</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>18338.593</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>16541.3366</v>
+        <v>15922.8885</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>22379.4554</v>
+        <v>21542.7315</v>
       </c>
       <c r="H4" s="32" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -1929,15 +1929,73 @@
         <v>22379.46</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="43" t="n"/>
-      <c r="C16" s="43" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="43" t="n"/>
-      <c r="K16" s="43" t="n"/>
-      <c r="L16" s="9" t="n"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>238</v>
+      </c>
+      <c r="E16" s="37" t="n">
+        <v>16689.04</v>
+      </c>
+      <c r="F16" s="37" t="n">
+        <v>3942.17</v>
+      </c>
+      <c r="G16" s="37" t="n">
+        <v>20631.21</v>
+      </c>
+      <c r="H16" s="37" t="n">
+        <v>18338.59</v>
+      </c>
+      <c r="I16" s="39" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="J16" s="36" t="inlineStr">
+        <is>
+          <t>/10</t>
+        </is>
+      </c>
+      <c r="K16" s="39" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="L16" s="37" t="n">
+        <v>18732.81</v>
+      </c>
+      <c r="M16" s="37" t="n">
+        <v>15922.89</v>
+      </c>
+      <c r="N16" s="37" t="n">
+        <v>21542.73</v>
+      </c>
+      <c r="O16" s="42" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P16" s="37" t="n">
+        <v>2043.77</v>
+      </c>
+      <c r="Q16" s="51" t="n">
+        <v>16689.04</v>
+      </c>
+      <c r="R16" s="51" t="n">
+        <v>15922.89</v>
+      </c>
+      <c r="S16" s="51" t="n">
+        <v>18338.59</v>
+      </c>
+      <c r="T16" s="51" t="n">
+        <v>21542.73</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -2957,7 +3015,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="30" t="inlineStr">
         <is>
-          <t>🎯 VR 5.0 현재 30단계 매수/매도 그물망 가이드( 26.10.12)</t>
+          <t>🎯 VR 5.0 현재 30단계 매수/매도 그물망 가이드( 26.10.19)</t>
         </is>
       </c>
     </row>
@@ -3021,25 +3079,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="48" t="n">
-        <v>80.37</v>
+        <v>69.44</v>
       </c>
       <c r="C5" s="48" t="n">
-        <v>241.12</v>
+        <v>69.44</v>
       </c>
       <c r="D5" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="47" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="48" t="n">
-        <v>82.78</v>
+        <v>71.52</v>
       </c>
       <c r="H5" s="48" t="n">
-        <v>331.14</v>
+        <v>500.62</v>
       </c>
       <c r="I5" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3047,25 +3105,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="48" t="n">
-        <v>79.7</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="C6" s="48" t="n">
-        <v>239.1</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="D6" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="47" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>83.72</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="H6" s="48" t="n">
-        <v>334.87</v>
+        <v>506.27</v>
       </c>
       <c r="I6" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -3073,25 +3131,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="48" t="n">
-        <v>79.02</v>
+        <v>68.27</v>
       </c>
       <c r="C7" s="48" t="n">
-        <v>237.07</v>
+        <v>68.27</v>
       </c>
       <c r="D7" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="47" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="48" t="n">
-        <v>84.66</v>
+        <v>73.14</v>
       </c>
       <c r="H7" s="48" t="n">
-        <v>338.65</v>
+        <v>511.98</v>
       </c>
       <c r="I7" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -3099,25 +3157,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="48" t="n">
-        <v>78.34999999999999</v>
+        <v>67.69</v>
       </c>
       <c r="C8" s="48" t="n">
-        <v>235.04</v>
+        <v>67.69</v>
       </c>
       <c r="D8" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" s="47" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="48" t="n">
-        <v>85.62</v>
+        <v>73.97</v>
       </c>
       <c r="H8" s="48" t="n">
-        <v>342.47</v>
+        <v>517.76</v>
       </c>
       <c r="I8" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3125,25 +3183,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="48" t="n">
-        <v>77.67</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="C9" s="48" t="n">
-        <v>233.02</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D9" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="47" t="n">
         <v>5</v>
       </c>
       <c r="G9" s="48" t="n">
-        <v>86.58</v>
+        <v>74.8</v>
       </c>
       <c r="H9" s="48" t="n">
-        <v>346.33</v>
+        <v>523.6</v>
       </c>
       <c r="I9" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3151,25 +3209,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="48" t="n">
-        <v>77</v>
+        <v>66.52</v>
       </c>
       <c r="C10" s="48" t="n">
-        <v>230.99</v>
+        <v>66.52</v>
       </c>
       <c r="D10" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="47" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="48" t="n">
-        <v>87.56</v>
+        <v>75.64</v>
       </c>
       <c r="H10" s="48" t="n">
-        <v>350.24</v>
+        <v>529.5</v>
       </c>
       <c r="I10" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -3177,25 +3235,25 @@
         <v>7</v>
       </c>
       <c r="B11" s="48" t="n">
-        <v>76.31999999999999</v>
+        <v>65.94</v>
       </c>
       <c r="C11" s="48" t="n">
-        <v>228.97</v>
+        <v>65.94</v>
       </c>
       <c r="D11" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" s="47" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="48" t="n">
-        <v>88.55</v>
+        <v>76.5</v>
       </c>
       <c r="H11" s="48" t="n">
-        <v>354.19</v>
+        <v>535.47</v>
       </c>
       <c r="I11" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -3203,25 +3261,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="48" t="n">
-        <v>75.65000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="C12" s="48" t="n">
-        <v>226.94</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="D12" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" s="47" t="n">
         <v>8</v>
       </c>
       <c r="G12" s="48" t="n">
-        <v>89.55</v>
+        <v>77.36</v>
       </c>
       <c r="H12" s="48" t="n">
-        <v>358.18</v>
+        <v>541.51</v>
       </c>
       <c r="I12" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3229,25 +3287,25 @@
         <v>9</v>
       </c>
       <c r="B13" s="48" t="n">
-        <v>74.97</v>
+        <v>64.77</v>
       </c>
       <c r="C13" s="48" t="n">
-        <v>224.91</v>
+        <v>64.77</v>
       </c>
       <c r="D13" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" s="47" t="n">
         <v>9</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>90.56</v>
+        <v>78.23</v>
       </c>
       <c r="H13" s="48" t="n">
-        <v>362.22</v>
+        <v>547.62</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -3255,25 +3313,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="48" t="n">
-        <v>74.3</v>
+        <v>64.19</v>
       </c>
       <c r="C14" s="48" t="n">
-        <v>222.89</v>
+        <v>64.19</v>
       </c>
       <c r="D14" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="G14" s="48" t="n">
-        <v>91.58</v>
+        <v>79.11</v>
       </c>
       <c r="H14" s="48" t="n">
-        <v>366.31</v>
+        <v>553.8</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -3281,25 +3339,25 @@
         <v>11</v>
       </c>
       <c r="B15" s="48" t="n">
-        <v>73.62</v>
+        <v>63.6</v>
       </c>
       <c r="C15" s="48" t="n">
-        <v>220.86</v>
+        <v>63.6</v>
       </c>
       <c r="D15" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" s="47" t="n">
         <v>11</v>
       </c>
       <c r="G15" s="48" t="n">
-        <v>92.61</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="H15" s="48" t="n">
-        <v>370.44</v>
+        <v>560.04</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -3307,25 +3365,25 @@
         <v>12</v>
       </c>
       <c r="B16" s="48" t="n">
-        <v>72.94</v>
+        <v>63.02</v>
       </c>
       <c r="C16" s="48" t="n">
-        <v>218.83</v>
+        <v>63.02</v>
       </c>
       <c r="D16" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" s="47" t="n">
         <v>12</v>
       </c>
       <c r="G16" s="48" t="n">
-        <v>93.65000000000001</v>
+        <v>80.91</v>
       </c>
       <c r="H16" s="48" t="n">
-        <v>374.62</v>
+        <v>566.36</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3333,25 +3391,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="48" t="n">
-        <v>72.27</v>
+        <v>62.43</v>
       </c>
       <c r="C17" s="48" t="n">
-        <v>216.81</v>
+        <v>62.43</v>
       </c>
       <c r="D17" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" s="47" t="n">
         <v>13</v>
       </c>
       <c r="G17" s="48" t="n">
-        <v>94.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H17" s="48" t="n">
-        <v>378.84</v>
+        <v>572.75</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -3359,25 +3417,25 @@
         <v>14</v>
       </c>
       <c r="B18" s="48" t="n">
-        <v>71.59</v>
+        <v>61.85</v>
       </c>
       <c r="C18" s="48" t="n">
-        <v>214.78</v>
+        <v>61.85</v>
       </c>
       <c r="D18" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" s="47" t="n">
         <v>14</v>
       </c>
       <c r="G18" s="48" t="n">
-        <v>95.78</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="H18" s="48" t="n">
-        <v>383.11</v>
+        <v>579.21</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -3385,25 +3443,25 @@
         <v>15</v>
       </c>
       <c r="B19" s="48" t="n">
-        <v>70.92</v>
+        <v>61.27</v>
       </c>
       <c r="C19" s="48" t="n">
-        <v>212.76</v>
+        <v>61.27</v>
       </c>
       <c r="D19" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="47" t="n">
         <v>15</v>
       </c>
       <c r="G19" s="48" t="n">
-        <v>96.86</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="H19" s="48" t="n">
-        <v>387.43</v>
+        <v>585.74</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -3411,25 +3469,25 @@
         <v>16</v>
       </c>
       <c r="B20" s="48" t="n">
-        <v>70.23999999999999</v>
+        <v>60.68</v>
       </c>
       <c r="C20" s="48" t="n">
-        <v>210.73</v>
+        <v>60.68</v>
       </c>
       <c r="D20" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" s="47" t="n">
         <v>16</v>
       </c>
       <c r="G20" s="48" t="n">
-        <v>97.95</v>
+        <v>84.62</v>
       </c>
       <c r="H20" s="48" t="n">
-        <v>391.8</v>
+        <v>592.35</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -3437,25 +3495,25 @@
         <v>17</v>
       </c>
       <c r="B21" s="48" t="n">
-        <v>69.56999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="C21" s="48" t="n">
-        <v>208.7</v>
+        <v>60.1</v>
       </c>
       <c r="D21" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" s="47" t="n">
         <v>17</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>99.06</v>
+        <v>85.58</v>
       </c>
       <c r="H21" s="48" t="n">
-        <v>396.22</v>
+        <v>599.03</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -3463,25 +3521,25 @@
         <v>18</v>
       </c>
       <c r="B22" s="48" t="n">
-        <v>68.89</v>
+        <v>59.52</v>
       </c>
       <c r="C22" s="48" t="n">
-        <v>206.68</v>
+        <v>59.52</v>
       </c>
       <c r="D22" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="47" t="n">
         <v>18</v>
       </c>
       <c r="G22" s="48" t="n">
-        <v>100.17</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="H22" s="48" t="n">
-        <v>400.69</v>
+        <v>605.78</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -3489,25 +3547,25 @@
         <v>19</v>
       </c>
       <c r="B23" s="48" t="n">
-        <v>68.22</v>
+        <v>58.93</v>
       </c>
       <c r="C23" s="48" t="n">
-        <v>204.65</v>
+        <v>58.93</v>
       </c>
       <c r="D23" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" s="47" t="n">
         <v>19</v>
       </c>
       <c r="G23" s="48" t="n">
-        <v>101.3</v>
+        <v>87.52</v>
       </c>
       <c r="H23" s="48" t="n">
-        <v>405.21</v>
+        <v>612.62</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -3515,25 +3573,25 @@
         <v>20</v>
       </c>
       <c r="B24" s="48" t="n">
-        <v>67.54000000000001</v>
+        <v>58.35</v>
       </c>
       <c r="C24" s="48" t="n">
-        <v>202.62</v>
+        <v>58.35</v>
       </c>
       <c r="D24" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" s="47" t="n">
         <v>20</v>
       </c>
       <c r="G24" s="48" t="n">
-        <v>102.45</v>
+        <v>88.5</v>
       </c>
       <c r="H24" s="48" t="n">
-        <v>409.78</v>
+        <v>619.53</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -3541,25 +3599,25 @@
         <v>21</v>
       </c>
       <c r="B25" s="48" t="n">
-        <v>66.87</v>
+        <v>57.77</v>
       </c>
       <c r="C25" s="48" t="n">
-        <v>200.6</v>
+        <v>57.77</v>
       </c>
       <c r="D25" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" s="47" t="n">
         <v>21</v>
       </c>
       <c r="G25" s="48" t="n">
-        <v>103.6</v>
+        <v>89.5</v>
       </c>
       <c r="H25" s="48" t="n">
-        <v>414.4</v>
+        <v>626.51</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -3567,25 +3625,25 @@
         <v>22</v>
       </c>
       <c r="B26" s="48" t="n">
-        <v>66.19</v>
+        <v>57.18</v>
       </c>
       <c r="C26" s="48" t="n">
-        <v>198.57</v>
+        <v>57.18</v>
       </c>
       <c r="D26" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="47" t="n">
         <v>22</v>
       </c>
       <c r="G26" s="48" t="n">
-        <v>104.77</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="H26" s="48" t="n">
-        <v>419.08</v>
+        <v>633.58</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -3593,25 +3651,25 @@
         <v>23</v>
       </c>
       <c r="B27" s="48" t="n">
-        <v>65.52</v>
+        <v>56.6</v>
       </c>
       <c r="C27" s="48" t="n">
-        <v>196.55</v>
+        <v>56.6</v>
       </c>
       <c r="D27" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" s="47" t="n">
         <v>23</v>
       </c>
       <c r="G27" s="48" t="n">
-        <v>105.95</v>
+        <v>91.53</v>
       </c>
       <c r="H27" s="48" t="n">
-        <v>423.8</v>
+        <v>640.73</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -3619,25 +3677,25 @@
         <v>24</v>
       </c>
       <c r="B28" s="48" t="n">
-        <v>64.84</v>
+        <v>56.02</v>
       </c>
       <c r="C28" s="48" t="n">
-        <v>194.52</v>
+        <v>56.02</v>
       </c>
       <c r="D28" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" s="47" t="n">
         <v>24</v>
       </c>
       <c r="G28" s="48" t="n">
-        <v>107.15</v>
+        <v>92.56</v>
       </c>
       <c r="H28" s="48" t="n">
-        <v>428.58</v>
+        <v>647.95</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -3645,25 +3703,25 @@
         <v>25</v>
       </c>
       <c r="B29" s="48" t="n">
-        <v>64.16</v>
+        <v>55.43</v>
       </c>
       <c r="C29" s="48" t="n">
-        <v>192.49</v>
+        <v>55.43</v>
       </c>
       <c r="D29" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" s="47" t="n">
         <v>25</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>108.35</v>
+        <v>93.61</v>
       </c>
       <c r="H29" s="48" t="n">
-        <v>433.42</v>
+        <v>655.26</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -3671,25 +3729,25 @@
         <v>26</v>
       </c>
       <c r="B30" s="48" t="n">
-        <v>63.49</v>
+        <v>54.85</v>
       </c>
       <c r="C30" s="48" t="n">
-        <v>190.47</v>
+        <v>54.85</v>
       </c>
       <c r="D30" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" s="47" t="n">
         <v>26</v>
       </c>
       <c r="G30" s="48" t="n">
-        <v>109.58</v>
+        <v>94.66</v>
       </c>
       <c r="H30" s="48" t="n">
-        <v>438.31</v>
+        <v>662.65</v>
       </c>
       <c r="I30" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -3697,25 +3755,25 @@
         <v>27</v>
       </c>
       <c r="B31" s="48" t="n">
-        <v>62.81</v>
+        <v>54.27</v>
       </c>
       <c r="C31" s="48" t="n">
-        <v>188.44</v>
+        <v>54.27</v>
       </c>
       <c r="D31" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" s="47" t="n">
         <v>27</v>
       </c>
       <c r="G31" s="48" t="n">
-        <v>110.81</v>
+        <v>95.73</v>
       </c>
       <c r="H31" s="48" t="n">
-        <v>443.25</v>
+        <v>670.13</v>
       </c>
       <c r="I31" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -3723,25 +3781,25 @@
         <v>28</v>
       </c>
       <c r="B32" s="48" t="n">
-        <v>62.14</v>
+        <v>53.68</v>
       </c>
       <c r="C32" s="48" t="n">
-        <v>186.41</v>
+        <v>53.68</v>
       </c>
       <c r="D32" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="47" t="n">
         <v>28</v>
       </c>
       <c r="G32" s="48" t="n">
-        <v>112.06</v>
+        <v>96.81</v>
       </c>
       <c r="H32" s="48" t="n">
-        <v>448.25</v>
+        <v>677.6799999999999</v>
       </c>
       <c r="I32" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -3749,25 +3807,25 @@
         <v>29</v>
       </c>
       <c r="B33" s="48" t="n">
-        <v>61.46</v>
+        <v>53.1</v>
       </c>
       <c r="C33" s="48" t="n">
-        <v>184.39</v>
+        <v>53.1</v>
       </c>
       <c r="D33" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" s="47" t="n">
         <v>29</v>
       </c>
       <c r="G33" s="48" t="n">
-        <v>113.33</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H33" s="48" t="n">
-        <v>453.31</v>
+        <v>685.33</v>
       </c>
       <c r="I33" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -3775,25 +3833,25 @@
         <v>30</v>
       </c>
       <c r="B34" s="48" t="n">
-        <v>60.79</v>
+        <v>52.52</v>
       </c>
       <c r="C34" s="48" t="n">
-        <v>182.36</v>
+        <v>52.52</v>
       </c>
       <c r="D34" s="49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="47" t="n">
         <v>30</v>
       </c>
       <c r="G34" s="48" t="n">
-        <v>114.6</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="H34" s="48" t="n">
-        <v>458.42</v>
+        <v>693.0599999999999</v>
       </c>
       <c r="I34" s="49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
